--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1034,7 +1034,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.22</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
         <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.78</v>
+        <v>2.35</v>
       </c>
       <c r="M27" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.78</v>
+        <v>2.55</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6260,16 +6260,16 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,22 +4994,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>1.54</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="n">

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2708,10 +2708,10 @@
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.78</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.98</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>2.33</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="M35" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>6</v>
+        <v>5.25</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,10 +5072,10 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB35" t="n">
         <v>2.28</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.74</v>
+        <v>2.17</v>
       </c>
       <c r="M42" t="n">
-        <v>3.6</v>
+        <v>2.75</v>
       </c>
       <c r="N42" t="n">
-        <v>4.6</v>
+        <v>4.02</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6260,16 +6260,16 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6392,16 +6392,16 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL46"/>
+  <dimension ref="A1:AL43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45887.5</v>
+        <v>45887.53125</v>
       </c>
     </row>
     <row r="8">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45887.53125</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="10">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2613,27 +2613,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="18">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>2.35</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>1.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="20">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.08</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
         <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4065,27 +4065,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,16 +4148,16 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="30">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="33">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.7</v>
+        <v>2.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>2.85</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>2.13</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="34">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4989,27 +4989,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="36">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="38">
@@ -5385,27 +5385,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="39">
@@ -5517,27 +5517,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>2.17</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>4.02</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="41">
@@ -5781,27 +5781,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="M42" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N42" t="n">
-        <v>4.02</v>
+        <v>2.34</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6168,403 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45887.83333333334</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Cuniburo</t>
-        </is>
-      </c>
-      <c r="G44" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0</v>
-      </c>
-      <c r="P44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="n">
-        <v>0</v>
-      </c>
-      <c r="X44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y44" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL44" s="3" t="n">
         <v>45887.875</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Brazil Serie B</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Athletic Club</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Criciúma</t>
-        </is>
-      </c>
-      <c r="G45" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L45" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="M45" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="N45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
-        <v>45887.875</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H46" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L46" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL46" s="3" t="n">
-        <v>45887.95833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL43"/>
+  <dimension ref="A1:AL48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,12 +1293,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1416,7 +1416,7 @@
         </is>
       </c>
       <c r="AL7" s="3" t="n">
-        <v>45887.53125</v>
+        <v>45887.5</v>
       </c>
     </row>
     <row r="8">
@@ -1557,12 +1557,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1680,7 +1680,7 @@
         </is>
       </c>
       <c r="AL9" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.53125</v>
       </c>
     </row>
     <row r="10">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.22</v>
+        <v>3.5</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N10" t="n">
-        <v>3.15</v>
+        <v>1.85</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,16 +1778,16 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2180,10 +2180,10 @@
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2613,12 +2613,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="18">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2877,12 +2877,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         </is>
       </c>
       <c r="AL19" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="20">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="M20" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N20" t="n">
-        <v>2.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.78</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>2.98</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>2.78</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.26</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>3.02</v>
       </c>
       <c r="N24" t="n">
-        <v>8.199999999999999</v>
+        <v>3.16</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,22 +3620,22 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,58 +3974,58 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M27" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N27" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4065,27 +4065,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4188,7 +4188,7 @@
         </is>
       </c>
       <c r="AL28" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="29">
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="30">
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4682,10 +4682,10 @@
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="33">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.55</v>
+        <v>4.7</v>
       </c>
       <c r="M33" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N33" t="n">
-        <v>2.85</v>
+        <v>1.75</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.13</v>
+        <v>2.2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="34">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>5.25</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.28</v>
+        <v>2.13</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="36">
@@ -5121,27 +5121,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.55</v>
+        <v>1.57</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>2.8</v>
+        <v>5.25</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="38">
@@ -5385,27 +5385,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5480,10 +5480,10 @@
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="39">
@@ -5517,27 +5517,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>4.02</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.28</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="40">
@@ -5649,27 +5649,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="41">
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5876,10 +5876,10 @@
         <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>3.2</v>
+        <v>2.17</v>
       </c>
       <c r="M42" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="N42" t="n">
-        <v>2.34</v>
+        <v>4.02</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.37</v>
+        <v>2.28</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,130 +6045,790 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Ypiranga Erechim</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Botafogo PB</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>0</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL43" s="3" t="n">
+        <v>45887.8125</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Brazil Serie C</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Tombense</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Caxias</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>0</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
+      </c>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="n">
+        <v>0</v>
+      </c>
+      <c r="X44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL44" s="3" t="n">
+        <v>45887.8125</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Brazil Serie A</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Mirassol</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Cruzeiro</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M45" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N45" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL45" s="3" t="n">
+        <v>45887.83333333334</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>21:00</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M46" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>0</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL46" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
         <is>
           <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="E47" t="inlineStr">
         <is>
           <t>Deportivo Cuenca</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Cuniburo</t>
         </is>
       </c>
-      <c r="G43" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" t="inlineStr">
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL43" s="3" t="n">
+      <c r="L47" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL47" s="3" t="n">
         <v>45887.875</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL48" s="3" t="n">
+        <v>45887.95833333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,22 +1694,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1784,10 +1784,10 @@
         <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.26</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>6</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>8.199999999999999</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,16 +3098,16 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,58 +3578,58 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N24" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC24" t="n">
         <v>2.3</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.16</v>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="M36" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N36" t="n">
-        <v>5.25</v>
+        <v>6</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5744,10 +5744,10 @@
         <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.49</v>
+        <v>4.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.32</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="M42" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="N42" t="n">
-        <v>4.02</v>
+        <v>3.75</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6446,7 +6446,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6524,16 +6524,16 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6656,16 +6656,16 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB47" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AC47" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>4.99</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1916,10 +1916,10 @@
         <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>1.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.08</v>
+        <v>1.26</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>1.89</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.35</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.55</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>2.78</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>2.78</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
         <v>2.3</v>
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.26</v>
+        <v>2.08</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5126,22 +5126,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5204,16 +5204,16 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1778,10 +1778,10 @@
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2444,10 +2444,10 @@
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N20" t="n">
         <v>2.35</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.55</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N21" t="n">
-        <v>2.35</v>
+        <v>2.55</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M24" t="n">
         <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.78</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>2.98</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.78</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3752,10 +3752,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4160,10 +4160,10 @@
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,22 +4862,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="M34" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.85</v>
+        <v>6</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.7</v>
+        <v>1.56</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M41" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,22 +3014,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.07</v>
       </c>
       <c r="M20" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.35</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,7 +3098,7 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC20" t="n">
         <v>2.3</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.55</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>2.35</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>2.55</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.08</v>
+        <v>2.78</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>8.199999999999999</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.89</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>2.08</v>
       </c>
       <c r="M26" t="n">
         <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>4.3</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.05</v>
+        <v>1.76</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.67</v>
+        <v>1.93</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5258,7 +5258,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5606,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M40" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N40" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,16 +5738,16 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD40" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M41" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N41" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL48"/>
+  <dimension ref="A1:AL50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -765,7 +765,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -888,7 +888,7 @@
         </is>
       </c>
       <c r="AL3" s="3" t="n">
-        <v>45887.375</v>
+        <v>45887.35416666666</v>
       </c>
     </row>
     <row r="4">
@@ -1029,27 +1029,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>45887.5</v>
+        <v>45887.45833333334</v>
       </c>
     </row>
     <row r="6">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1548,7 +1548,7 @@
         </is>
       </c>
       <c r="AL8" s="3" t="n">
-        <v>45887.53125</v>
+        <v>45887.5</v>
       </c>
     </row>
     <row r="9">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1812,7 +1812,7 @@
         </is>
       </c>
       <c r="AL10" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.53125</v>
       </c>
     </row>
     <row r="11">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2048,10 +2048,10 @@
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2868,7 +2868,7 @@
         </is>
       </c>
       <c r="AL18" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3009,27 +3009,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.53</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3132,7 +3132,7 @@
         </is>
       </c>
       <c r="AL20" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="21">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.35</v>
+        <v>1.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="N22" t="n">
-        <v>2.55</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.08</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N23" t="n">
-        <v>2.35</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,16 +3494,16 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>2.98</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>2.78</v>
+        <v>4.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,10 +3620,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>4.1</v>
+        <v>2.7</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,22 +3884,22 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4197,12 +4197,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4320,7 +4320,7 @@
         </is>
       </c>
       <c r="AL29" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="30">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="32">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4766,13 +4766,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N33" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="34">
@@ -4857,27 +4857,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4940,16 +4940,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="AL34" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="35">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="36">
@@ -5294,14 +5294,14 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="N37" t="n">
         <v>2.55</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N37" t="n">
-        <v>2.85</v>
-      </c>
       <c r="O37" t="n">
         <v>0</v>
       </c>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.13</v>
+        <v>1.84</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.7</v>
+        <v>1.86</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5385,12 +5385,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5508,7 +5508,7 @@
         </is>
       </c>
       <c r="AL38" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="39">
@@ -5517,27 +5517,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.55</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>2.8</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.77</v>
+        <v>1.56</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         </is>
       </c>
       <c r="AL39" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="40">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="41">
@@ -5781,27 +5781,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="M41" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N41" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,16 +5870,16 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD41" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="42">
@@ -5913,12 +5913,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M42" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="N42" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,16 +6002,16 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="43">
@@ -6045,27 +6045,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.09</v>
+        <v>4.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="44">
@@ -6177,12 +6177,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6192,12 +6192,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="M44" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="N44" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="45">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.2</v>
+        <v>2.44</v>
       </c>
       <c r="M45" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.34</v>
+        <v>2.89</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="46">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="AL46" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="47">
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="M47" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N47" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6656,16 +6656,16 @@
         <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA47" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.87</v>
+        <v>2.37</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="AL47" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="48">
@@ -6705,129 +6705,393 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M48" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N48" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="n">
+        <v>0</v>
+      </c>
+      <c r="X48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z48" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA48" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC48" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL48" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Cuniburo</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>0</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
+      </c>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="n">
+        <v>0</v>
+      </c>
+      <c r="X49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL49" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C50" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
+      <c r="D50" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" t="inlineStr">
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L48" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M48" t="n">
-        <v>3.78</v>
-      </c>
-      <c r="N48" t="n">
-        <v>4.99</v>
-      </c>
-      <c r="O48" t="n">
-        <v>0</v>
-      </c>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="n">
-        <v>0</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB48" t="n">
+      <c r="L50" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M50" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N50" t="n">
+        <v>5</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB50" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AC50" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL48" s="3" t="n">
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>2.81</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
         <v>2.3</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="M22" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="N22" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,22 +3356,22 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3674,22 +3674,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,10 +3758,10 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>2.07</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,16 +3884,16 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.48</v>
+        <v>1.53</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4280,16 +4280,16 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4730,7 +4730,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL50"/>
+  <dimension ref="A1:AL51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,16 +2702,16 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.95</v>
+        <v>1.26</v>
       </c>
       <c r="M21" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,16 +3356,16 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3500,10 +3500,10 @@
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,7 +3890,7 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
         <v>2.3</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>8.199999999999999</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4329,27 +4329,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="AL30" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="31">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4476,12 +4476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4584,7 +4584,7 @@
         </is>
       </c>
       <c r="AL31" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4608,12 +4608,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="33">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5112,7 +5112,7 @@
         </is>
       </c>
       <c r="AL35" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="36">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.48</v>
+        <v>4.33</v>
       </c>
       <c r="M36" t="n">
-        <v>3.07</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>2.55</v>
+        <v>1.69</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.84</v>
+        <v>2.2</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.86</v>
+        <v>1.67</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="37">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5649,12 +5649,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="AL40" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="41">
@@ -5913,27 +5913,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6008,10 +6008,10 @@
         <v>0</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="AL42" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="43">
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N43" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,16 +6134,16 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE43" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6177,27 +6177,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.1</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>2.65</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>3.75</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,10 +6266,10 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>2.28</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.58</v>
+        <v>1.81</v>
       </c>
       <c r="AD44" t="n">
         <v>0</v>
@@ -6300,7 +6300,7 @@
         </is>
       </c>
       <c r="AL44" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="45">
@@ -6309,12 +6309,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="M45" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="N45" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,10 +6398,10 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD45" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="46">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M46" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N46" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6573,12 +6573,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>3.03</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6662,10 +6662,10 @@
         <v>0</v>
       </c>
       <c r="AB47" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC47" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD47" t="n">
         <v>0</v>
@@ -6696,7 +6696,7 @@
         </is>
       </c>
       <c r="AL47" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="48">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="M48" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N48" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="49">
@@ -6969,129 +6969,261 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N50" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>0</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
+      </c>
+      <c r="V50" t="n">
+        <v>0</v>
+      </c>
+      <c r="W50" t="n">
+        <v>0</v>
+      </c>
+      <c r="X50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z50" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA50" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC50" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AD50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL50" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" t="inlineStr">
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L50" t="n">
+      <c r="L51" t="n">
         <v>1.52</v>
       </c>
-      <c r="M50" t="n">
+      <c r="M51" t="n">
         <v>3.8</v>
       </c>
-      <c r="N50" t="n">
+      <c r="N51" t="n">
         <v>5</v>
       </c>
-      <c r="O50" t="n">
-        <v>0</v>
-      </c>
-      <c r="P50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0</v>
-      </c>
-      <c r="T50" t="n">
-        <v>0</v>
-      </c>
-      <c r="U50" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" t="n">
-        <v>0</v>
-      </c>
-      <c r="W50" t="n">
-        <v>0</v>
-      </c>
-      <c r="X50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y50" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB50" t="n">
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC50" t="n">
+      <c r="AC51" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL50" s="3" t="n">
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,7 +2354,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2364,12 +2364,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>2.31</v>
       </c>
       <c r="M15" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.26</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>6</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>8.199999999999999</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,16 +3890,16 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,7 +4022,7 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC27" t="n">
         <v>2.3</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.08</v>
+        <v>1.65</v>
       </c>
       <c r="M29" t="n">
         <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>2.8</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4292,10 +4292,10 @@
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="M30" t="n">
-        <v>2.7</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="N38" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,22 +6050,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M43" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N43" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,16 +6134,16 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD43" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE43" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6842,7 +6842,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M49" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6920,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7052,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,22 +1826,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.47</v>
+        <v>2.31</v>
       </c>
       <c r="M11" t="n">
-        <v>3.63</v>
+        <v>2.97</v>
       </c>
       <c r="N11" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,16 +1910,16 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AD11" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.31</v>
+        <v>3.47</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD16" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.08</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>4.1</v>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,22 +3278,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3356,10 +3356,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3368,10 +3368,10 @@
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4.1</v>
+        <v>3.21</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,16 +3626,16 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3674,7 +3674,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>2.7</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>2.88</v>
       </c>
       <c r="N26" t="n">
-        <v>8.199999999999999</v>
+        <v>2.84</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2.1</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>2.7</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>3.75</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.53</v>
+        <v>2.48</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.65</v>
+        <v>2.07</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.65</v>
       </c>
       <c r="N29" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,16 +4286,16 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5258,22 +5258,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5336,16 +5336,16 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5732,16 +5732,16 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL51"/>
+  <dimension ref="A1:AL52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>2.97</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,16 +2438,16 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>3.47</v>
       </c>
       <c r="M16" t="n">
-        <v>2.81</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>4.1</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,10 +3488,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="M24" t="n">
-        <v>3.21</v>
+        <v>2.7</v>
       </c>
       <c r="N24" t="n">
-        <v>2.73</v>
+        <v>3.75</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,16 +3620,16 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>2.48</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.26</v>
+        <v>2.08</v>
       </c>
       <c r="M25" t="n">
-        <v>6</v>
+        <v>4.1</v>
       </c>
       <c r="N25" t="n">
-        <v>8.199999999999999</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.89</v>
+        <v>1.76</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.7</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>2.88</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,10 +3884,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -3896,10 +3896,10 @@
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4016,16 +4016,16 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4286,10 +4286,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4593,27 +4593,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4716,7 +4716,7 @@
         </is>
       </c>
       <c r="AL32" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="33">
@@ -4725,12 +4725,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4848,7 +4848,7 @@
         </is>
       </c>
       <c r="AL33" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="34">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5244,7 +5244,7 @@
         </is>
       </c>
       <c r="AL36" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="37">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5294,13 +5294,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5342,10 +5342,10 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD37" t="n">
         <v>0</v>
@@ -5376,7 +5376,7 @@
         </is>
       </c>
       <c r="AL37" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="38">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5732,16 +5732,16 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5781,12 +5781,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5904,7 +5904,7 @@
         </is>
       </c>
       <c r="AL41" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="42">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
         </is>
       </c>
       <c r="AL43" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="44">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6309,12 +6309,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>2.65</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>3.75</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6432,7 +6432,7 @@
         </is>
       </c>
       <c r="AL45" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="46">
@@ -6441,12 +6441,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.44</v>
+        <v>2.1</v>
       </c>
       <c r="M46" t="n">
-        <v>3</v>
+        <v>2.65</v>
       </c>
       <c r="N46" t="n">
-        <v>2.89</v>
+        <v>3.75</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6530,10 +6530,10 @@
         <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AD46" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
         </is>
       </c>
       <c r="AL46" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="47">
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6705,12 +6705,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>3.03</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6794,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="n">
         <v>0</v>
@@ -6828,7 +6828,7 @@
         </is>
       </c>
       <c r="AL48" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="49">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6878,13 +6878,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.23</v>
+        <v>3.03</v>
       </c>
       <c r="M49" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>3.25</v>
+        <v>2.22</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -6920,16 +6920,16 @@
         <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AD49" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
         </is>
       </c>
       <c r="AL49" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="50">
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7052,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7101,129 +7101,261 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Cuniburo</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>0</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
+      </c>
+      <c r="V51" t="n">
+        <v>0</v>
+      </c>
+      <c r="W51" t="n">
+        <v>0</v>
+      </c>
+      <c r="X51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL51" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" t="inlineStr">
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L51" t="n">
+      <c r="L52" t="n">
         <v>1.52</v>
       </c>
-      <c r="M51" t="n">
+      <c r="M52" t="n">
         <v>3.8</v>
       </c>
-      <c r="N51" t="n">
+      <c r="N52" t="n">
         <v>5</v>
       </c>
-      <c r="O51" t="n">
-        <v>0</v>
-      </c>
-      <c r="P51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="n">
-        <v>0</v>
-      </c>
-      <c r="V51" t="n">
-        <v>0</v>
-      </c>
-      <c r="W51" t="n">
-        <v>0</v>
-      </c>
-      <c r="X51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB51" t="n">
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
         <v>1.79</v>
       </c>
-      <c r="AC51" t="n">
+      <c r="AC52" t="n">
         <v>1.87</v>
       </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="n">
+      <c r="AD52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AL52" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -674,13 +674,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.75</v>
+        <v>3.28</v>
       </c>
       <c r="M2" t="n">
-        <v>3.2</v>
+        <v>3.71</v>
       </c>
       <c r="N2" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -728,10 +728,10 @@
         <v>1.87</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>3.63</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>2.81</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,16 +3224,16 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.65</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>4.3</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3371,7 +3371,7 @@
         <v>2.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.1</v>
+        <v>2.95</v>
       </c>
       <c r="M24" t="n">
-        <v>2.7</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.75</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3620,16 +3620,16 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>2.48</v>
+        <v>1.63</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.08</v>
+        <v>1.8</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.76</v>
+        <v>2.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.93</v>
+        <v>1.67</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>2.1</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="N26" t="n">
-        <v>8.199999999999999</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,22 +3884,22 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4028,10 +4028,10 @@
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,10 +4154,10 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4370,10 +4370,10 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
         <v>3.1</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5030,13 +5030,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -5078,10 +5078,10 @@
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="M39" t="n">
         <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5600,10 +5600,10 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="AB39" t="n">
         <v>2.28</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5738,10 +5738,10 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5796,12 +5796,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5870,10 +5870,10 @@
         <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="M46" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="N46" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6524,10 +6524,10 @@
         <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB46" t="n">
         <v>2.28</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -6974,7 +6974,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6984,12 +6984,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7010,13 +7010,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N50" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7052,16 +7052,16 @@
         <v>0</v>
       </c>
       <c r="Z50" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA50" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AD50" t="n">
         <v>0</v>
@@ -7106,7 +7106,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7116,12 +7116,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7142,13 +7142,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7184,16 +7184,16 @@
         <v>0</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD51" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,22 +1958,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,16 +2042,16 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,10 +2306,10 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>3.47</v>
       </c>
       <c r="M16" t="n">
-        <v>2.81</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>8.5</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3236,10 +3236,10 @@
         <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,7 +3410,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3420,12 +3420,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,22 +3542,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,64 +3578,64 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD24" t="n">
         <v>2.05</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3758,16 +3758,16 @@
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
         <v>2.05</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3884,16 +3884,16 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.28</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>5.6</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,16 +4148,16 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4280,10 +4280,10 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4418,10 +4418,10 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,22 +5522,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5558,13 +5558,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5600,16 +5600,16 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC39" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD39" t="n">
         <v>0</v>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5664,12 +5664,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,22 +1166,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1862,13 +1862,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1910,10 +1910,10 @@
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.35</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2570,16 +2570,16 @@
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2618,22 +2618,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,7 +2750,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,10 +2834,10 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.28</v>
+        <v>2.95</v>
       </c>
       <c r="M21" t="n">
-        <v>5.6</v>
+        <v>3.41</v>
       </c>
       <c r="N21" t="n">
-        <v>8.5</v>
+        <v>2.05</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3230,16 +3230,16 @@
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3632,10 +3632,10 @@
         <v>2.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3710,13 +3710,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>8.5</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3764,10 +3764,10 @@
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,64 +3974,64 @@
         </is>
       </c>
       <c r="L27" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M27" t="n">
+        <v>4</v>
+      </c>
+      <c r="N27" t="n">
         <v>2.95</v>
       </c>
-      <c r="M27" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.05</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,7 +4070,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4080,12 +4080,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4148,22 +4148,22 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4334,7 +4334,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4344,12 +4344,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1298,22 +1298,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1382,10 +1382,10 @@
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2222,22 +2222,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2258,13 +2258,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2306,16 +2306,16 @@
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2750,22 +2750,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.61</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
-        <v>2.81</v>
+        <v>3.63</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2834,16 +2834,16 @@
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.53</v>
+        <v>2.4</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,22 +3146,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,64 +3182,64 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.95</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
         <v>2.05</v>
       </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3494,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3806,7 +3806,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,22 +3938,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,16 +4022,16 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,22 +4202,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="M29" t="n">
         <v>2.7</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.88</v>
-      </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>3.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4280,16 +4280,16 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="N30" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5390,22 +5390,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5426,13 +5426,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5468,16 +5468,16 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5732,16 +5732,16 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AC40" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -902,22 +902,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1166,7 +1166,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1176,12 +1176,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1250,10 +1250,10 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1440,12 +1440,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1466,13 +1466,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1514,10 +1514,10 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,7 +1958,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1968,12 +1968,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1994,13 +1994,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -2090,22 +2090,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2126,13 +2126,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2174,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
@@ -2222,7 +2222,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2354,22 +2354,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2390,13 +2390,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2438,10 +2438,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
         <v>0</v>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2654,13 +2654,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2702,10 +2702,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD17" t="n">
         <v>0</v>
@@ -2882,7 +2882,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2966,10 +2966,10 @@
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
         <v>0</v>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3050,13 +3050,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3098,10 +3098,10 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
         <v>0</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3156,12 +3156,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3182,13 +3182,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>2.1</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="N21" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3224,22 +3224,22 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3288,12 +3288,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3314,13 +3314,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3362,16 +3362,16 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3410,22 +3410,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3446,13 +3446,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3488,16 +3488,16 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
         <v>0</v>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3552,12 +3552,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3578,13 +3578,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3626,10 +3626,10 @@
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
         <v>0</v>
@@ -3806,22 +3806,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3842,13 +3842,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3890,10 +3890,10 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="n">
         <v>0</v>
@@ -3938,7 +3938,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3974,13 +3974,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4022,10 +4022,10 @@
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
         <v>0</v>
@@ -4070,22 +4070,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4106,13 +4106,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4154,16 +4154,16 @@
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4202,7 +4202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4212,12 +4212,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4238,13 +4238,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4280,22 +4280,22 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4334,22 +4334,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4412,16 +4412,16 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="n">
         <v>0</v>
@@ -4466,22 +4466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4598,22 +4598,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4862,7 +4862,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4872,12 +4872,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4898,13 +4898,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4946,10 +4946,10 @@
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5136,12 +5136,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5162,13 +5162,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5210,10 +5210,10 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD36" t="n">
         <v>0</v>
@@ -5390,7 +5390,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5400,12 +5400,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5654,22 +5654,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5690,13 +5690,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.53</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -5732,16 +5732,16 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="AD40" t="n">
         <v>0</v>
@@ -5786,22 +5786,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5822,13 +5822,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>1.53</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>3.5</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>7</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -5864,16 +5864,16 @@
         <v>0</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="AD41" t="n">
         <v>0</v>
@@ -5918,7 +5918,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -5928,12 +5928,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6002,10 +6002,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AD42" t="n">
         <v>0</v>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6060,12 +6060,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6086,13 +6086,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6134,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD43" t="n">
         <v>0</v>
@@ -6182,22 +6182,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6218,13 +6218,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6266,16 +6266,16 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6314,22 +6314,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6350,13 +6350,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6398,16 +6398,16 @@
         <v>0</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6588,12 +6588,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6614,13 +6614,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N47" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -6720,12 +6720,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL52"/>
+  <dimension ref="A1:AO52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,115 +513,130 @@
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>Odd_A_HT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Under05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>homeGoals</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>awayGoals</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>Odd_H_HT1</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_D_HT1</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>homeGoals</t>
+          <t>Odd_A_HT1</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>awayGoals</t>
+          <t>Odd_DNB_H</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_DNB_A</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_H</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Odd_marcar_prim_A</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -710,28 +725,32 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1.79</v>
+        <v>0</v>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -745,17 +764,22 @@
       <c r="AI2" t="n">
         <v>0</v>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL2" s="3" t="n">
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" s="3" t="n">
         <v>45887.22916666666</v>
       </c>
     </row>
@@ -859,11 +883,15 @@
       <c r="AC3" t="n">
         <v>0</v>
       </c>
-      <c r="AD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>0</v>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
@@ -877,17 +905,22 @@
       <c r="AI3" t="n">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" s="3" t="n">
         <v>45887.35416666666</v>
       </c>
     </row>
@@ -991,11 +1024,15 @@
       <c r="AC4" t="n">
         <v>0</v>
       </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -1009,17 +1046,22 @@
       <c r="AI4" t="n">
         <v>0</v>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" s="3" t="n">
         <v>45887.45833333334</v>
       </c>
     </row>
@@ -1123,11 +1165,15 @@
       <c r="AC5" t="n">
         <v>0</v>
       </c>
-      <c r="AD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>0</v>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1141,17 +1187,22 @@
       <c r="AI5" t="n">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL5" s="3" t="n">
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="3" t="n">
         <v>45887.45833333334</v>
       </c>
     </row>
@@ -1238,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1250,16 +1301,20 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1273,17 +1328,22 @@
       <c r="AI6" t="n">
         <v>0</v>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="3" t="n">
         <v>45887.5</v>
       </c>
     </row>
@@ -1387,11 +1447,15 @@
       <c r="AC7" t="n">
         <v>0</v>
       </c>
-      <c r="AD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>0</v>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
@@ -1405,17 +1469,22 @@
       <c r="AI7" t="n">
         <v>0</v>
       </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL7" s="3" t="n">
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="3" t="n">
         <v>45887.5</v>
       </c>
     </row>
@@ -1519,11 +1588,15 @@
       <c r="AC8" t="n">
         <v>0</v>
       </c>
-      <c r="AD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>0</v>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
@@ -1537,17 +1610,22 @@
       <c r="AI8" t="n">
         <v>0</v>
       </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="3" t="n">
         <v>45887.5</v>
       </c>
     </row>
@@ -1651,11 +1729,15 @@
       <c r="AC9" t="n">
         <v>0</v>
       </c>
-      <c r="AD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>0</v>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -1669,17 +1751,22 @@
       <c r="AI9" t="n">
         <v>0</v>
       </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="3" t="n">
         <v>45887.53125</v>
       </c>
     </row>
@@ -1783,11 +1870,15 @@
       <c r="AC10" t="n">
         <v>0</v>
       </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1801,17 +1892,22 @@
       <c r="AI10" t="n">
         <v>0</v>
       </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="3" t="n">
         <v>45887.53125</v>
       </c>
     </row>
@@ -1915,11 +2011,15 @@
       <c r="AC11" t="n">
         <v>0</v>
       </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -1933,17 +2033,22 @@
       <c r="AI11" t="n">
         <v>0</v>
       </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL11" s="3" t="n">
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2047,11 +2152,15 @@
       <c r="AC12" t="n">
         <v>0</v>
       </c>
-      <c r="AD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>0</v>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -2065,17 +2174,22 @@
       <c r="AI12" t="n">
         <v>0</v>
       </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL12" s="3" t="n">
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2179,11 +2293,15 @@
       <c r="AC13" t="n">
         <v>0</v>
       </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -2197,17 +2315,22 @@
       <c r="AI13" t="n">
         <v>0</v>
       </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2311,11 +2434,15 @@
       <c r="AC14" t="n">
         <v>0</v>
       </c>
-      <c r="AD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>0</v>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
@@ -2329,17 +2456,22 @@
       <c r="AI14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2426,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2438,16 +2570,20 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -2461,17 +2597,22 @@
       <c r="AI15" t="n">
         <v>0</v>
       </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL15" s="3" t="n">
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2575,11 +2716,15 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>0</v>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
@@ -2593,17 +2738,22 @@
       <c r="AI16" t="n">
         <v>0</v>
       </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2690,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2702,16 +2852,20 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
@@ -2725,17 +2879,22 @@
       <c r="AI17" t="n">
         <v>0</v>
       </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL17" s="3" t="n">
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2822,28 +2981,32 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.6</v>
+        <v>0</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -2857,17 +3020,22 @@
       <c r="AI18" t="n">
         <v>0</v>
       </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL18" s="3" t="n">
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="3" t="n">
         <v>45887.54166666666</v>
       </c>
     </row>
@@ -2971,11 +3139,15 @@
       <c r="AC19" t="n">
         <v>0</v>
       </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -2989,17 +3161,22 @@
       <c r="AI19" t="n">
         <v>0</v>
       </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL19" s="3" t="n">
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="3" t="n">
         <v>45887.5625</v>
       </c>
     </row>
@@ -3086,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3098,16 +3275,20 @@
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3121,17 +3302,22 @@
       <c r="AI20" t="n">
         <v>0</v>
       </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL20" s="3" t="n">
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="3" t="n">
         <v>45887.5625</v>
       </c>
     </row>
@@ -3212,34 +3398,38 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3253,17 +3443,22 @@
       <c r="AI21" t="n">
         <v>0</v>
       </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL21" s="3" t="n">
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -3350,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3362,16 +3557,20 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3385,17 +3584,22 @@
       <c r="AI22" t="n">
         <v>0</v>
       </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL22" s="3" t="n">
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -3476,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -3488,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3499,11 +3703,15 @@
       <c r="AC23" t="n">
         <v>0</v>
       </c>
-      <c r="AD23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>0</v>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
@@ -3517,17 +3725,22 @@
       <c r="AI23" t="n">
         <v>0</v>
       </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL23" s="3" t="n">
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -3631,11 +3844,15 @@
       <c r="AC24" t="n">
         <v>0</v>
       </c>
-      <c r="AD24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>0</v>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
@@ -3649,17 +3866,22 @@
       <c r="AI24" t="n">
         <v>0</v>
       </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL24" s="3" t="n">
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -3752,10 +3974,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -3763,11 +3985,15 @@
       <c r="AC25" t="n">
         <v>0</v>
       </c>
-      <c r="AD25" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.8</v>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
@@ -3781,17 +4007,22 @@
       <c r="AI25" t="n">
         <v>0</v>
       </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL25" s="3" t="n">
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -3878,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -3890,16 +4121,20 @@
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
@@ -3913,17 +4148,22 @@
       <c r="AI26" t="n">
         <v>0</v>
       </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL26" s="3" t="n">
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -4027,11 +4267,15 @@
       <c r="AC27" t="n">
         <v>0</v>
       </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
@@ -4045,17 +4289,22 @@
       <c r="AI27" t="n">
         <v>0</v>
       </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL27" s="3" t="n">
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -4142,28 +4391,32 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.67</v>
+        <v>0</v>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
@@ -4177,17 +4430,22 @@
       <c r="AI28" t="n">
         <v>0</v>
       </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL28" s="3" t="n">
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -4280,10 +4538,10 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4291,11 +4549,15 @@
       <c r="AC29" t="n">
         <v>0</v>
       </c>
-      <c r="AD29" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.68</v>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
@@ -4309,17 +4571,22 @@
       <c r="AI29" t="n">
         <v>0</v>
       </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL29" s="3" t="n">
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -4406,10 +4673,10 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4418,16 +4685,20 @@
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4441,17 +4712,22 @@
       <c r="AI30" t="n">
         <v>0</v>
       </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL30" s="3" t="n">
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
       </c>
     </row>
@@ -4555,11 +4831,15 @@
       <c r="AC31" t="n">
         <v>0</v>
       </c>
-      <c r="AD31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>0</v>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
@@ -4573,17 +4853,22 @@
       <c r="AI31" t="n">
         <v>0</v>
       </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL31" s="3" t="n">
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" s="3" t="n">
         <v>45887.60416666666</v>
       </c>
     </row>
@@ -4687,11 +4972,15 @@
       <c r="AC32" t="n">
         <v>0</v>
       </c>
-      <c r="AD32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>0</v>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF32" t="n">
         <v>0</v>
@@ -4705,17 +4994,22 @@
       <c r="AI32" t="n">
         <v>0</v>
       </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL32" s="3" t="n">
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" s="3" t="n">
         <v>45887.60416666666</v>
       </c>
     </row>
@@ -4819,11 +5113,15 @@
       <c r="AC33" t="n">
         <v>0</v>
       </c>
-      <c r="AD33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>0</v>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF33" t="n">
         <v>0</v>
@@ -4837,17 +5135,22 @@
       <c r="AI33" t="n">
         <v>0</v>
       </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL33" s="3" t="n">
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" s="3" t="n">
         <v>45887.61458333334</v>
       </c>
     </row>
@@ -4951,11 +5254,15 @@
       <c r="AC34" t="n">
         <v>0</v>
       </c>
-      <c r="AD34" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>0</v>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF34" t="n">
         <v>0</v>
@@ -4969,17 +5276,22 @@
       <c r="AI34" t="n">
         <v>0</v>
       </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL34" s="3" t="n">
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" s="3" t="n">
         <v>45887.625</v>
       </c>
     </row>
@@ -5083,11 +5395,15 @@
       <c r="AC35" t="n">
         <v>0</v>
       </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF35" t="n">
         <v>0</v>
@@ -5101,17 +5417,22 @@
       <c r="AI35" t="n">
         <v>0</v>
       </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL35" s="3" t="n">
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" s="3" t="n">
         <v>45887.625</v>
       </c>
     </row>
@@ -5198,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5210,16 +5531,20 @@
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF36" t="n">
         <v>0</v>
@@ -5233,17 +5558,22 @@
       <c r="AI36" t="n">
         <v>0</v>
       </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL36" s="3" t="n">
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" s="3" t="n">
         <v>45887.625</v>
       </c>
     </row>
@@ -5330,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5342,16 +5672,20 @@
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF37" t="n">
         <v>0</v>
@@ -5365,17 +5699,22 @@
       <c r="AI37" t="n">
         <v>0</v>
       </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL37" s="3" t="n">
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" s="3" t="n">
         <v>45887.63541666666</v>
       </c>
     </row>
@@ -5479,11 +5818,15 @@
       <c r="AC38" t="n">
         <v>0</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF38" t="n">
         <v>0</v>
@@ -5497,17 +5840,22 @@
       <c r="AI38" t="n">
         <v>0</v>
       </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL38" s="3" t="n">
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" s="3" t="n">
         <v>45887.64583333334</v>
       </c>
     </row>
@@ -5611,11 +5959,15 @@
       <c r="AC39" t="n">
         <v>0</v>
       </c>
-      <c r="AD39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE39" t="n">
-        <v>0</v>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
@@ -5629,17 +5981,22 @@
       <c r="AI39" t="n">
         <v>0</v>
       </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL39" s="3" t="n">
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" s="3" t="n">
         <v>45887.64583333334</v>
       </c>
     </row>
@@ -5726,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -5738,16 +6095,20 @@
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AD40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE40" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
@@ -5761,17 +6122,22 @@
       <c r="AI40" t="n">
         <v>0</v>
       </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL40" s="3" t="n">
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" s="3" t="n">
         <v>45887.64583333334</v>
       </c>
     </row>
@@ -5852,34 +6218,38 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AB41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE41" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF41" t="n">
         <v>0</v>
@@ -5893,17 +6263,22 @@
       <c r="AI41" t="n">
         <v>0</v>
       </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL41" s="3" t="n">
+      <c r="AJ41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
       </c>
     </row>
@@ -6007,11 +6382,15 @@
       <c r="AC42" t="n">
         <v>0</v>
       </c>
-      <c r="AD42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE42" t="n">
-        <v>0</v>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF42" t="n">
         <v>0</v>
@@ -6025,17 +6404,22 @@
       <c r="AI42" t="n">
         <v>0</v>
       </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL42" s="3" t="n">
+      <c r="AJ42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO42" s="3" t="n">
         <v>45887.66666666666</v>
       </c>
     </row>
@@ -6122,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6134,16 +6518,20 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE43" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF43" t="n">
         <v>0</v>
@@ -6157,17 +6545,22 @@
       <c r="AI43" t="n">
         <v>0</v>
       </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL43" s="3" t="n">
+      <c r="AJ43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO43" s="3" t="n">
         <v>45887.66666666666</v>
       </c>
     </row>
@@ -6254,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6266,16 +6659,20 @@
         <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF44" t="n">
         <v>0</v>
@@ -6289,17 +6686,22 @@
       <c r="AI44" t="n">
         <v>0</v>
       </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL44" s="3" t="n">
+      <c r="AJ44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO44" s="3" t="n">
         <v>45887.67708333334</v>
       </c>
     </row>
@@ -6392,10 +6794,10 @@
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -6403,11 +6805,15 @@
       <c r="AC45" t="n">
         <v>0</v>
       </c>
-      <c r="AD45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AE45" t="n">
-        <v>1.92</v>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF45" t="n">
         <v>0</v>
@@ -6421,17 +6827,22 @@
       <c r="AI45" t="n">
         <v>0</v>
       </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL45" s="3" t="n">
+      <c r="AJ45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO45" s="3" t="n">
         <v>45887.67708333334</v>
       </c>
     </row>
@@ -6512,34 +6923,38 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AC46" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE46" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF46" t="n">
         <v>0</v>
@@ -6553,17 +6968,22 @@
       <c r="AI46" t="n">
         <v>0</v>
       </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL46" s="3" t="n">
+      <c r="AJ46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO46" s="3" t="n">
         <v>45887.70833333334</v>
       </c>
     </row>
@@ -6667,11 +7087,15 @@
       <c r="AC47" t="n">
         <v>0</v>
       </c>
-      <c r="AD47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE47" t="n">
-        <v>0</v>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF47" t="n">
         <v>0</v>
@@ -6685,17 +7109,22 @@
       <c r="AI47" t="n">
         <v>0</v>
       </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL47" s="3" t="n">
+      <c r="AJ47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO47" s="3" t="n">
         <v>45887.8125</v>
       </c>
     </row>
@@ -6799,11 +7228,15 @@
       <c r="AC48" t="n">
         <v>0</v>
       </c>
-      <c r="AD48" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE48" t="n">
-        <v>0</v>
+      <c r="AD48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE48" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF48" t="n">
         <v>0</v>
@@ -6817,17 +7250,22 @@
       <c r="AI48" t="n">
         <v>0</v>
       </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL48" s="3" t="n">
+      <c r="AJ48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO48" s="3" t="n">
         <v>45887.8125</v>
       </c>
     </row>
@@ -6914,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -6926,16 +7364,20 @@
         <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AD49" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE49" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF49" t="n">
         <v>0</v>
@@ -6949,17 +7391,22 @@
       <c r="AI49" t="n">
         <v>0</v>
       </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL49" s="3" t="n">
+      <c r="AJ49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO49" s="3" t="n">
         <v>45887.83333333334</v>
       </c>
     </row>
@@ -7063,11 +7510,15 @@
       <c r="AC50" t="n">
         <v>0</v>
       </c>
-      <c r="AD50" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE50" t="n">
-        <v>0</v>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF50" t="n">
         <v>0</v>
@@ -7081,17 +7532,22 @@
       <c r="AI50" t="n">
         <v>0</v>
       </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL50" s="3" t="n">
+      <c r="AJ50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO50" s="3" t="n">
         <v>45887.875</v>
       </c>
     </row>
@@ -7172,34 +7628,38 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AA51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AD51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE51" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF51" t="n">
         <v>0</v>
@@ -7213,17 +7673,22 @@
       <c r="AI51" t="n">
         <v>0</v>
       </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL51" s="3" t="n">
+      <c r="AJ51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO51" s="3" t="n">
         <v>45887.875</v>
       </c>
     </row>
@@ -7310,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7322,16 +7787,20 @@
         <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE52" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AF52" t="n">
         <v>0</v>
@@ -7345,17 +7814,22 @@
       <c r="AI52" t="n">
         <v>0</v>
       </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AL52" s="3" t="n">
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,16 +2981,16 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.1</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>3.75</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3398,16 +3398,16 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.48</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.28</v>
+        <v>2.1</v>
       </c>
       <c r="M25" t="n">
-        <v>5.6</v>
+        <v>2.7</v>
       </c>
       <c r="N25" t="n">
-        <v>8.5</v>
+        <v>3.75</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3962,22 +3962,22 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,52 +4073,52 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
         <v>2.95</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.05</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5519,10 +5519,10 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
         <v>0</v>
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5936,16 +5936,16 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M44" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N44" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6716,22 +6716,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,16 +6788,16 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z45" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA45" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB45" t="n">
         <v>0</v>
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M47" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N47" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M50" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N51" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,16 +7628,16 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO52"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,16 +3680,16 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>2.2</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3962,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>8.5</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4244,10 +4244,10 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
         <v>0</v>
@@ -4256,10 +4256,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Y29" t="n">
         <v>2.3</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4640,10 +4640,10 @@
         <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4673,16 +4673,16 @@
         <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5019,12 +5019,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5151,7 +5151,7 @@
         <v>0</v>
       </c>
       <c r="AO33" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="34">
@@ -5160,12 +5160,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5201,13 +5201,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -5237,10 +5237,10 @@
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z34" t="n">
         <v>0</v>
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="35">
@@ -5583,12 +5583,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>4.33</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>1.69</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5715,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="AO37" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="38">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="39">
@@ -5870,22 +5870,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>1.53</v>
+        <v>2.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.5</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5936,16 +5936,16 @@
         <v>0</v>
       </c>
       <c r="V39" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6288,12 +6288,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6420,7 +6420,7 @@
         <v>0</v>
       </c>
       <c r="AO42" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="43">
@@ -6570,27 +6570,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6653,10 +6653,10 @@
         <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
         <v>0</v>
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="AO44" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M46" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="N46" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6923,22 +6923,22 @@
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="47">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.44</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="N47" t="n">
-        <v>2.89</v>
+        <v>3.95</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7064,16 +7064,16 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W47" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X47" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y47" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M48" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>3.03</v>
+        <v>2.09</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>2.22</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="50">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.01</v>
+        <v>3.03</v>
       </c>
       <c r="M50" t="n">
         <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>3.55</v>
+        <v>2.22</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.75</v>
+        <v>2.37</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="51">
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,16 +7628,16 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7698,138 +7698,279 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Cuniburo</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
+      </c>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="n">
+        <v>0</v>
+      </c>
+      <c r="X52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO52" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G52" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" t="inlineStr">
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L52" t="n">
+      <c r="L53" t="n">
         <v>1.52</v>
       </c>
-      <c r="M52" t="n">
+      <c r="M53" t="n">
         <v>3.8</v>
       </c>
-      <c r="N52" t="n">
+      <c r="N53" t="n">
         <v>5</v>
       </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="n">
-        <v>0</v>
-      </c>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="n">
-        <v>0</v>
-      </c>
-      <c r="X52" t="n">
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
         <v>1.79</v>
       </c>
-      <c r="Y52" t="n">
+      <c r="Y53" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN52" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO52" s="3" t="n">
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,22 +1499,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1635,12 +1635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1767,7 +1767,7 @@
         <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45887.53125</v>
+        <v>45887.5</v>
       </c>
     </row>
     <row r="10">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1917,7 +1917,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.53125</v>
       </c>
     </row>
     <row r="12">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,16 +2558,16 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3327,27 +3327,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,16 +3404,16 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="22">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,52 +3509,52 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.05</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>2.72</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>3.72</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,22 +3680,22 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,16 +4109,16 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>2.26</v>
       </c>
       <c r="M27" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>2.73</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4737,27 +4737,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,16 +4949,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="33">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -5301,27 +5301,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="36">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="37">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="39">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.48</v>
+        <v>2.02</v>
       </c>
       <c r="M39" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N39" t="n">
-        <v>2.55</v>
+        <v>3.3</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -5997,7 +5997,7 @@
         <v>0</v>
       </c>
       <c r="AO39" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="40">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,13 +6047,13 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
@@ -6083,10 +6083,10 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y40" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z40" t="n">
         <v>0</v>
@@ -6138,7 +6138,7 @@
         <v>0</v>
       </c>
       <c r="AO40" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="41">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6561,7 +6561,7 @@
         <v>0</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="44">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6702,7 +6702,7 @@
         <v>0</v>
       </c>
       <c r="AO44" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="45">
@@ -6711,12 +6711,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6843,7 +6843,7 @@
         <v>0</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6852,27 +6852,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,16 +6929,16 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA46" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB46" t="n">
         <v>0</v>
@@ -6984,7 +6984,7 @@
         <v>0</v>
       </c>
       <c r="AO46" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="47">
@@ -6993,27 +6993,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>4.8</v>
       </c>
       <c r="M47" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="N47" t="n">
-        <v>3.95</v>
+        <v>1.62</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7064,16 +7064,16 @@
         <v>0</v>
       </c>
       <c r="V47" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W47" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>2.28</v>
+        <v>1.91</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="Z47" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         <v>0</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="48">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="M48" t="n">
-        <v>3</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7217,10 +7217,10 @@
         <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="M49" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7346,16 +7346,16 @@
         <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="50">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.03</v>
+        <v>2.44</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>2.22</v>
+        <v>2.89</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7493,10 +7493,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="51">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.01</v>
+        <v>2.09</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,16 +7628,16 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X51" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,13 +7739,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="M52" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7775,10 +7775,10 @@
         <v>0</v>
       </c>
       <c r="X52" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y52" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z52" t="n">
         <v>0</v>
@@ -7830,7 +7830,7 @@
         <v>0</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7839,138 +7839,420 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ecuador Primera Categoría Serie A</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Deportivo Cuenca</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Cuniburo</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
+      </c>
+      <c r="V53" t="n">
+        <v>0</v>
+      </c>
+      <c r="W53" t="n">
+        <v>0</v>
+      </c>
+      <c r="X53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L54" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N54" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>0</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W54" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C55" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D55" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="L55" t="n">
         <v>1.52</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M55" t="n">
         <v>3.8</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N55" t="n">
         <v>5</v>
       </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>0</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
+      </c>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" t="n">
         <v>1.79</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y55" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="3" t="n">
+      <c r="Z55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,16 +2417,16 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.61</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
-        <v>2.81</v>
+        <v>3.63</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,16 +2981,16 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="Y18" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA18" t="n">
         <v>1.53</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,52 +3509,52 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="M22" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.8</v>
-      </c>
-      <c r="M22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N22" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,22 +3680,22 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>3.21</v>
       </c>
       <c r="N24" t="n">
-        <v>8.5</v>
+        <v>2.73</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,7 +4250,7 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Y27" t="n">
         <v>2.3</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>2.88</v>
+        <v>3.75</v>
       </c>
       <c r="N29" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="M31" t="n">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="N31" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4808,16 +4808,16 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,16 +4949,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X41" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N42" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N50" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,10 +2699,10 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
         <v>0</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,16 +2981,16 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3539,10 +3539,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3680,16 +3680,16 @@
         <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.95</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.05</v>
+        <v>3.72</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X27" t="n">
-        <v>1.63</v>
+        <v>2.48</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,16 +4391,16 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4499,10 +4499,10 @@
         <v>2.03</v>
       </c>
       <c r="M29" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.1</v>
+        <v>2.95</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4532,16 +4532,16 @@
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.95</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4808,22 +4808,22 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,10 +4955,10 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5942,10 +5942,10 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z39" t="n">
         <v>0</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6500,16 +6500,16 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -7275,7 +7275,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -7331,19 +7331,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V49" t="n">
         <v>1.6</v>
@@ -7358,16 +7358,16 @@
         <v>1.58</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.72916666666</v>
       </c>
     </row>
     <row r="50">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8051,16 +8051,16 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="M12" t="n">
-        <v>3.63</v>
+        <v>2.81</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,16 +2135,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,13 +2522,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3539,22 +3539,22 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Y25" t="n">
         <v>2.3</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4244,16 +4244,16 @@
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>2.48</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.07</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>2.72</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>3.72</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4526,22 +4526,22 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4679,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,16 +4814,16 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>2.88</v>
       </c>
       <c r="N32" t="n">
-        <v>2.05</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,16 +4949,16 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6365,10 +6365,10 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6500,16 +6500,16 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.09</v>
+        <v>2.44</v>
       </c>
       <c r="M50" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="N50" t="n">
-        <v>3.4</v>
+        <v>2.89</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="M51" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>2.89</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,13 +1394,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1430,10 +1430,10 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>0</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,13 +2099,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2135,10 +2135,10 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,16 +2699,16 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,13 +2804,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="M19" t="n">
-        <v>3.63</v>
+        <v>2.81</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,16 +3122,16 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,13 +3227,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -3263,10 +3263,10 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
         <v>0</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,13 +3368,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -3404,10 +3404,10 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
         <v>0</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3551,10 +3551,10 @@
         <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.95</v>
+        <v>2.26</v>
       </c>
       <c r="M25" t="n">
-        <v>3.41</v>
+        <v>3.21</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>2.73</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Y25" t="n">
         <v>2.3</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4115,10 +4115,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,13 +4214,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>2.05</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -4250,10 +4250,10 @@
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z27" t="n">
         <v>0</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4532,10 +4532,10 @@
         <v>2.15</v>
       </c>
       <c r="X29" t="n">
-        <v>2.48</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,13 +4778,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4814,10 +4814,10 @@
         <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M32" t="n">
-        <v>2.88</v>
+        <v>3.8</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,22 +4949,22 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6224,10 +6224,10 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6641,16 +6641,16 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,13 +7034,13 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>4.8</v>
+        <v>2.75</v>
       </c>
       <c r="M47" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="N47" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
         <v>0</v>
@@ -7070,16 +7070,16 @@
         <v>0</v>
       </c>
       <c r="X47" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="Y47" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z47" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA47" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AB47" t="n">
         <v>0</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>4.3</v>
       </c>
       <c r="N48" t="n">
-        <v>2.3</v>
+        <v>1.55</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7211,16 +7211,16 @@
         <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -7352,10 +7352,10 @@
         <v>2.2</v>
       </c>
       <c r="X49" t="n">
-        <v>2.28</v>
+        <v>2.9</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="Z49" t="n">
         <v>5.3</v>
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -7598,10 +7598,10 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.09</v>
+        <v>2.18</v>
       </c>
       <c r="M51" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
         <v>3.4</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W51" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8051,16 +8051,16 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,13 +1253,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1289,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,13 +1535,13 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -1571,10 +1571,10 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
         <v>0</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,13 +2381,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2417,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
         <v>0</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,13 +2663,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2699,16 +2699,16 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -3122,10 +3122,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>3.21</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,13 +3650,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>2.95</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3692,10 +3692,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>1.28</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>5.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>8.5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="M25" t="n">
-        <v>3.21</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,52 +4214,52 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.05</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.07</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="N29" t="n">
-        <v>3.72</v>
+        <v>2.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4526,16 +4526,16 @@
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="W29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="M30" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4667,16 +4667,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4955,16 +4955,16 @@
         <v>0</v>
       </c>
       <c r="X32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X41" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,13 +6611,13 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
@@ -6647,10 +6647,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="Z44" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8051,16 +8051,16 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -689,19 +689,19 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.71</v>
+        <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="n">
         <v>1.91</v>
@@ -759,13 +759,13 @@
         <v>0</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -774,10 +774,10 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO2" s="3" t="n">
         <v>45887.22916666666</v>
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1262,31 +1262,31 @@
         <v>2.62</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X6" t="n">
         <v>2.05</v>
@@ -1295,16 +1295,16 @@
         <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1464,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45887.5</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,13 +2240,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.61</v>
+        <v>2.31</v>
       </c>
       <c r="M14" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X14" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2981,10 +2981,10 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
         <v>0</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3236,31 +3236,31 @@
         <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="X20" t="n">
         <v>2.17</v>
@@ -3269,16 +3269,16 @@
         <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.5625</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,13 +3509,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3833,10 +3833,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3962,16 +3962,16 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X25" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,95 +4073,95 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M26" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="W26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z26" t="n">
         <v>2.05</v>
       </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y26" t="n">
+      <c r="AA26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN26" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,40 +4214,40 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X27" t="n">
         <v>1.6</v>
@@ -4256,16 +4256,16 @@
         <v>2.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.05</v>
+        <v>2.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,83 +4496,83 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M29" t="n">
+        <v>4</v>
+      </c>
+      <c r="N29" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W29" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y29" t="n">
         <v>2.7</v>
       </c>
-      <c r="M29" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N29" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="O29" t="n">
-        <v>0</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI29" t="n">
         <v>2.5</v>
       </c>
-      <c r="X29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,13 +4637,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M30" t="n">
-        <v>2.72</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4667,16 +4667,16 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="Z30" t="n">
         <v>0</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,46 +4778,46 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4848,13 +4848,13 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,58 +4919,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M32" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>45887.58333333334</v>
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W50" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W51" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N53" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M54" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8051,16 +8051,16 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W54" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X54" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45887.5</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>2.31</v>
       </c>
       <c r="M12" t="n">
-        <v>3.63</v>
+        <v>2.97</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>2.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>3.75</v>
+        <v>2.63</v>
       </c>
       <c r="S12" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="T12" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>1.39</v>
       </c>
       <c r="W12" t="n">
-        <v>4.7</v>
+        <v>2.6</v>
       </c>
       <c r="X12" t="n">
-        <v>1.5</v>
+        <v>2.35</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>4.1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>1.16</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,31 +2163,31 @@
         </is>
       </c>
       <c r="AF12" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>2.25</v>
-      </c>
       <c r="AN12" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,22 +2486,22 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45887.54166666666</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,46 +3509,46 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
         <v>0</v>
@@ -3557,10 +3557,10 @@
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,13 +3791,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3827,10 +3827,10 @@
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
         <v>0</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3962,10 +3962,10 @@
         <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
         <v>0</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4</v>
+      </c>
+      <c r="N26" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="O26" t="n">
         <v>1.8</v>
       </c>
-      <c r="M26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="O26" t="n">
-        <v>1.62</v>
-      </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="T26" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="U26" t="n">
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="W26" t="n">
-        <v>4.2</v>
+        <v>5.35</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="Z26" t="n">
         <v>2.05</v>
       </c>
       <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AH26" t="n">
-        <v>2.4</v>
+        <v>2.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.62</v>
+        <v>1.8</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.53</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W27" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P29" t="n">
         <v>2</v>
       </c>
       <c r="Q29" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R29" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V29" t="n">
         <v>1.25</v>
       </c>
-      <c r="R29" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S29" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1.09</v>
-      </c>
       <c r="W29" t="n">
-        <v>5.35</v>
+        <v>3.85</v>
       </c>
       <c r="X29" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4563,16 +4563,16 @@
         <v>1.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,7 +4581,7 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AN29" t="n">
         <v>2</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.95</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="X30" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.3</v>
+        <v>2.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,46 +4778,46 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
         <v>0</v>
@@ -4826,10 +4826,10 @@
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4848,13 +4848,13 @@
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,95 +4919,95 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="M32" t="n">
-        <v>5.6</v>
+        <v>3.75</v>
       </c>
       <c r="N32" t="n">
-        <v>8.5</v>
+        <v>3.1</v>
       </c>
       <c r="O32" t="n">
-        <v>1.33</v>
+        <v>1.73</v>
       </c>
       <c r="P32" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="R32" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="S32" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="T32" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="U32" t="n">
         <v>1.01</v>
       </c>
       <c r="V32" t="n">
-        <v>1.07</v>
+        <v>1.16</v>
       </c>
       <c r="W32" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="X32" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>1.42</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AC32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF32" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN32" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AD32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE32" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF32" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI32" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AJ32" t="n">
-        <v>7</v>
-      </c>
-      <c r="AK32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM32" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN32" t="n">
-        <v>3.25</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>45887.58333333334</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,13 +6188,13 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -6218,16 +6218,16 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="Z41" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,13 +6329,13 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
         <v>0</v>
@@ -6359,16 +6359,16 @@
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,13 +6752,13 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
         <v>0</v>
@@ -6788,10 +6788,10 @@
         <v>0</v>
       </c>
       <c r="X45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Z45" t="n">
         <v>0</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,13 +6893,13 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
@@ -6929,10 +6929,10 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Z46" t="n">
         <v>0</v>
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.18</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>3.4</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,10 +7487,10 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="W50" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="X50" t="n">
         <v>0</v>
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N51" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,10 +7628,10 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W51" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="X51" t="n">
         <v>0</v>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="M53" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,13 +8021,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N54" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -8051,16 +8051,16 @@
         <v>0</v>
       </c>
       <c r="V54" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X54" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z54" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,31 +1253,31 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -1289,22 +1289,22 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1323,13 +1323,13 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1358,22 +1358,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,31 +1394,31 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1430,22 +1430,22 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1464,13 +1464,13 @@
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45887.5</v>
@@ -1640,7 +1640,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,58 +1676,58 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1740,19 +1740,19 @@
         </is>
       </c>
       <c r="AF9" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45887.5</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45887.54166666666</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45887.54166666666</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.5625</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.5625</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,59 +3509,59 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.07</v>
+        <v>1.28</v>
       </c>
       <c r="M22" t="n">
-        <v>2.72</v>
+        <v>5.6</v>
       </c>
       <c r="N22" t="n">
-        <v>3.72</v>
+        <v>8.5</v>
       </c>
       <c r="O22" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="Q22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.67</v>
       </c>
-      <c r="R22" t="n">
+      <c r="AC22" t="n">
         <v>2.1</v>
       </c>
-      <c r="S22" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W22" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD22" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="AH22" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.83</v>
+        <v>2.88</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.75</v>
+        <v>7</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.91</v>
+        <v>1.33</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.5</v>
+        <v>3.25</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M24" t="n">
+        <v>4</v>
+      </c>
+      <c r="N24" t="n">
         <v>2.95</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W24" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z24" t="n">
         <v>2.05</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="n">
-        <v>0</v>
-      </c>
-      <c r="T24" t="n">
-        <v>0</v>
-      </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
-      <c r="W24" t="n">
-        <v>0</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>0</v>
-      </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V26" t="n">
         <v>1.25</v>
       </c>
-      <c r="R26" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.09</v>
-      </c>
       <c r="W26" t="n">
-        <v>5.35</v>
+        <v>3.85</v>
       </c>
       <c r="X26" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4140,16 +4140,16 @@
         <v>1.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>2.07</v>
       </c>
       <c r="M27" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>3.72</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="W27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="X27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2.5</v>
       </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4284,13 +4284,13 @@
         <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.8</v>
+        <v>2.95</v>
       </c>
       <c r="M28" t="n">
-        <v>3.8</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>3.8</v>
+        <v>2.05</v>
       </c>
       <c r="O28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q28" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="W28" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Z28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.28</v>
+        <v>1.8</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>3.8</v>
       </c>
       <c r="N30" t="n">
-        <v>8.5</v>
+        <v>3.8</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="U30" t="n">
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.07</v>
+        <v>1.15</v>
       </c>
       <c r="W30" t="n">
-        <v>5.75</v>
+        <v>4.2</v>
       </c>
       <c r="X30" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.67</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.05</v>
+        <v>1.24</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.48</v>
+        <v>1.94</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>2.4</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="AJ30" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.33</v>
+        <v>1.62</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,58 +4919,58 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M32" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N32" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
         <v>1.53</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W32" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="X32" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y32" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="inlineStr">
         <is>
@@ -4983,19 +4983,19 @@
         </is>
       </c>
       <c r="AF32" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AJ32" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AK32" t="n">
         <v>0</v>
@@ -5004,10 +5004,10 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
         <v>45887.58333333334</v>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5660,10 +5660,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z37" t="n">
         <v>0</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5780,43 +5780,43 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5829,19 +5829,19 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -6188,58 +6188,58 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="M41" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S41" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X41" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z41" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA41" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB41" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AC41" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -6252,19 +6252,19 @@
         </is>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AG41" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AH41" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI41" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,46 +6329,46 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N42" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z42" t="n">
         <v>0</v>
@@ -6377,10 +6377,10 @@
         <v>0</v>
       </c>
       <c r="AB42" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -6399,13 +6399,13 @@
         <v>0</v>
       </c>
       <c r="AH42" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
@@ -6500,16 +6500,16 @@
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W43" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X43" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Y43" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,58 +6611,58 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="M44" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="N44" t="n">
-        <v>2.55</v>
+        <v>3.34</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X44" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -6675,19 +6675,19 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AO44" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6752,58 +6752,58 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X45" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z45" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA45" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB45" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -6837,10 +6837,10 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO45" s="3" t="n">
         <v>45887.66666666666</v>
@@ -6902,31 +6902,31 @@
         <v>2.8</v>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W46" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="X46" t="n">
         <v>2.05</v>
@@ -6935,16 +6935,16 @@
         <v>1.77</v>
       </c>
       <c r="Z46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA46" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB46" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC46" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AD46" t="inlineStr">
         <is>
@@ -6957,19 +6957,19 @@
         </is>
       </c>
       <c r="AF46" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG46" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH46" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI46" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
@@ -6978,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN46" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO46" s="3" t="n">
         <v>45887.66666666666</v>
@@ -7184,31 +7184,31 @@
         <v>1.55</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="X48" t="n">
         <v>1.97</v>
@@ -7217,16 +7217,16 @@
         <v>1.83</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -7239,19 +7239,19 @@
         </is>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -7260,10 +7260,10 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO48" s="3" t="n">
         <v>45887.67708333334</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.2</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>3.9</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="P6" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.25</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>3.75</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>1.62</v>
+        <v>1.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X6" t="n">
-        <v>1.53</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.33</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.15</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.61</v>
+        <v>1.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH6" t="n">
-        <v>4.5</v>
+        <v>3.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.5</v>
+        <v>2.13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>2.2</v>
+        <v>3.38</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.38</v>
+        <v>2.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45887.5</v>
@@ -1640,22 +1640,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Oulu</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1712,22 +1712,22 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1746,13 +1746,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,10 +1761,10 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO9" s="3" t="n">
         <v>45887.5</v>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,58 +2522,58 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="AF15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>2.31</v>
       </c>
       <c r="M17" t="n">
-        <v>2.81</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>2.85</v>
       </c>
       <c r="O17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="W17" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.83</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="S17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,31 +2868,31 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="AI17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AJ17" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AN17" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,22 +2909,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,95 +2945,95 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.47</v>
+        <v>2.61</v>
       </c>
       <c r="M18" t="n">
-        <v>3.63</v>
+        <v>2.81</v>
       </c>
       <c r="N18" t="n">
-        <v>1.8</v>
+        <v>2.62</v>
       </c>
       <c r="O18" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="P18" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="R18" t="n">
-        <v>3.75</v>
+        <v>2.38</v>
       </c>
       <c r="S18" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="T18" t="n">
-        <v>1.62</v>
+        <v>1.29</v>
       </c>
       <c r="U18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>2.4</v>
+        <v>1.53</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AC18" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN18" t="n">
         <v>2.38</v>
-      </c>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>1.62</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45887.54166666666</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.5625</v>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.5625</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,83 +3509,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="P22" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.2</v>
+        <v>1.57</v>
       </c>
       <c r="R22" t="n">
-        <v>4.33</v>
+        <v>2.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2</v>
+        <v>3.54</v>
       </c>
       <c r="T22" t="n">
-        <v>1.73</v>
+        <v>1.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="V22" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>1.4</v>
+        <v>2.47</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.88</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI22" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>2.88</v>
-      </c>
       <c r="AJ22" t="n">
-        <v>7</v>
+        <v>3.64</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AN22" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,19 +3650,19 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="O23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q23" t="n">
         <v>1.3</v>
@@ -3680,10 +3680,10 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W23" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="X23" t="n">
         <v>1.6</v>
@@ -3692,16 +3692,16 @@
         <v>2.2</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.69</v>
+        <v>1.94</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="AI23" t="n">
         <v>2.38</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>2.26</v>
       </c>
       <c r="M24" t="n">
-        <v>4</v>
+        <v>3.21</v>
       </c>
       <c r="N24" t="n">
-        <v>2.95</v>
+        <v>2.73</v>
       </c>
       <c r="O24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="P24" t="n">
         <v>2</v>
       </c>
       <c r="Q24" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R24" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V24" t="n">
         <v>1.25</v>
       </c>
-      <c r="R24" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="S24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T24" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1.09</v>
-      </c>
       <c r="W24" t="n">
-        <v>5.35</v>
+        <v>3.85</v>
       </c>
       <c r="X24" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.68</v>
+        <v>1.4</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3858,16 +3858,16 @@
         <v>1.4</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AN24" t="n">
         <v>2</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,7 +4037,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.26</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.21</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.73</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
         <v>2</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="S26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC26" t="n">
         <v>2.63</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W26" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.2</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4140,16 +4140,16 @@
         <v>1.4</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,7 +4158,7 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AN26" t="n">
         <v>2</v>
@@ -4178,7 +4178,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.07</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>2.72</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>3.72</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P27" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W27" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="R27" t="n">
+      <c r="AA27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN27" t="n">
         <v>2.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W27" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="X27" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.5</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,13 +4355,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -4391,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
         <v>0</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,46 +4496,46 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4544,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="M30" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="O30" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="P30" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="R30" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="T30" t="n">
-        <v>1.53</v>
+        <v>1.73</v>
       </c>
       <c r="U30" t="n">
         <v>1.01</v>
       </c>
       <c r="V30" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="W30" t="n">
-        <v>4.2</v>
+        <v>5.75</v>
       </c>
       <c r="X30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.2</v>
+        <v>2.88</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB30" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.24</v>
+        <v>1.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.94</v>
+        <v>3.48</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.4</v>
+        <v>1.67</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="AJ30" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4883,7 +4883,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4919,13 +4919,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4949,10 +4949,10 @@
         <v>0</v>
       </c>
       <c r="V32" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X32" t="n">
         <v>0</v>
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5175,12 +5175,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5306,22 +5306,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5780,43 +5780,43 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W38" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC38" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5829,19 +5829,19 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AJ38" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,13 +5906,13 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M39" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -5921,43 +5921,43 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S39" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X39" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA39" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD39" t="inlineStr">
         <is>
@@ -5970,19 +5970,19 @@
         </is>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG39" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH39" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI39" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ39" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -6293,7 +6293,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,58 +6329,58 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.48</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>2.55</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R42" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S42" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V42" t="n">
         <v>1.4</v>
       </c>
-      <c r="R42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X42" t="n">
-        <v>1.84</v>
+        <v>2.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.86</v>
+        <v>1.54</v>
       </c>
       <c r="Z42" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.73</v>
+        <v>1.98</v>
       </c>
       <c r="AC42" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -6393,19 +6393,19 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG42" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH42" t="n">
-        <v>3.25</v>
+        <v>2.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AJ42" t="n">
-        <v>3.1</v>
+        <v>4.15</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AN42" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6434,22 +6434,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,46 +6470,46 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="M43" t="n">
-        <v>3.41</v>
+        <v>3.07</v>
       </c>
       <c r="N43" t="n">
-        <v>6.3</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.28</v>
+        <v>1.84</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="Z43" t="n">
         <v>0</v>
@@ -6518,10 +6518,10 @@
         <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
@@ -6540,13 +6540,13 @@
         <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -6555,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN43" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO43" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6575,22 +6575,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,58 +6611,58 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="N44" t="n">
-        <v>3.34</v>
+        <v>6.3</v>
       </c>
       <c r="O44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W44" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="X44" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z44" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA44" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB44" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC44" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -6675,19 +6675,19 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH44" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI44" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ44" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO44" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,19 +6752,19 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
         <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
         <v>1.44</v>
@@ -6773,38 +6773,38 @@
         <v>2.63</v>
       </c>
       <c r="S45" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U45" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="V45" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W45" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X45" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AA45" t="n">
         <v>1.25</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="AF45" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AI45" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -6837,10 +6837,10 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AN45" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AO45" s="3" t="n">
         <v>45887.66666666666</v>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,19 +6893,19 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="M46" t="n">
         <v>3.3</v>
       </c>
       <c r="N46" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O46" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P46" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q46" t="n">
         <v>1.44</v>
@@ -6914,38 +6914,38 @@
         <v>2.63</v>
       </c>
       <c r="S46" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W46" t="n">
         <v>3</v>
       </c>
-      <c r="T46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.1</v>
-      </c>
       <c r="X46" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Y46" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z46" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA46" t="n">
         <v>1.25</v>
       </c>
       <c r="AB46" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC46" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD46" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6957,19 +6957,19 @@
         </is>
       </c>
       <c r="AF46" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG46" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH46" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AI46" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ46" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK46" t="n">
         <v>0</v>
@@ -6978,10 +6978,10 @@
         <v>0</v>
       </c>
       <c r="AM46" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AN46" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AO46" s="3" t="n">
         <v>45887.66666666666</v>
@@ -6998,22 +6998,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,83 +7034,83 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M47" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O47" t="n">
+        <v>3</v>
+      </c>
+      <c r="P47" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R47" t="n">
+        <v>3</v>
+      </c>
+      <c r="S47" t="n">
         <v>2.75</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N47" t="n">
+      <c r="T47" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W47" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X47" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI47" t="n">
         <v>2.3</v>
       </c>
-      <c r="O47" t="n">
-        <v>0</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ47" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -7119,10 +7119,10 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AO47" s="3" t="n">
         <v>45887.67708333334</v>
@@ -7139,22 +7139,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,58 +7175,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="M48" t="n">
-        <v>4.3</v>
+        <v>3.95</v>
       </c>
       <c r="N48" t="n">
-        <v>1.55</v>
+        <v>2.3</v>
       </c>
       <c r="O48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Z48" t="n">
-        <v>3.3</v>
+        <v>1.88</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -7239,19 +7239,19 @@
         </is>
       </c>
       <c r="AF48" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AH48" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="AI48" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ48" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -7260,10 +7260,10 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
         <v>45887.67708333334</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AO53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="M2" t="n">
         <v>4</v>
       </c>
       <c r="N2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -789,7 +789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45887.35416666666</v>
+        <v>45887.375</v>
       </c>
     </row>
     <row r="4">
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1635,27 +1635,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oulu</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1676,31 +1676,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1712,22 +1712,22 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
@@ -1746,13 +1746,13 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
         <v>0</v>
@@ -1761,13 +1761,13 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AO9" s="3" t="n">
-        <v>45887.5</v>
+        <v>45887.53125</v>
       </c>
     </row>
     <row r="10">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1917,27 +1917,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2049,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
-        <v>45887.53125</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="12">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,22 +2204,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2381,10 +2381,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.47</v>
+        <v>3.74</v>
       </c>
       <c r="M14" t="n">
-        <v>3.63</v>
+        <v>3.84</v>
       </c>
       <c r="N14" t="n">
         <v>1.8</v>
@@ -2396,22 +2396,22 @@
         <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R14" t="n">
-        <v>3.75</v>
+        <v>3.28</v>
       </c>
       <c r="S14" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="T14" t="n">
         <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W14" t="n">
         <v>4.7</v>
@@ -2420,19 +2420,19 @@
         <v>1.5</v>
       </c>
       <c r="Y14" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC14" t="n">
         <v>2.4</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.38</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2454,10 +2454,10 @@
         <v>4</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,58 +2804,58 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2868,19 +2868,19 @@
         </is>
       </c>
       <c r="AF17" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.61</v>
+        <v>2.7</v>
       </c>
       <c r="M18" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="N18" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="P18" t="n">
         <v>1.83</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="Q18" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="R18" t="n">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="S18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X18" t="n">
-        <v>2.5</v>
+        <v>2.17</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB18" t="n">
-        <v>2.1</v>
+        <v>1.98</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AJ18" t="n">
-        <v>4.33</v>
+        <v>3.13</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,13 +3030,13 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="AN18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AN18" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AO18" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="19">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3177,7 +3177,7 @@
         <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="20">
@@ -3186,27 +3186,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,98 +3227,98 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
       <c r="O20" t="n">
-        <v>2.31</v>
+        <v>1.62</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>1.29</v>
       </c>
       <c r="R20" t="n">
-        <v>2.44</v>
+        <v>3.3</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="T20" t="n">
-        <v>1.27</v>
+        <v>1.54</v>
       </c>
       <c r="U20" t="n">
         <v>1.03</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>1.18</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>4.33</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>1.6</v>
       </c>
       <c r="Y20" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>2.31</v>
-      </c>
       <c r="AN20" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3327,27 +3327,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,13 +3453,13 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO21" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="22">
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,95 +3509,95 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>2.24</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>2.76</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>3.63</v>
       </c>
       <c r="O22" t="n">
-        <v>2.12</v>
+        <v>1.91</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="R22" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="S22" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="T22" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="U22" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="V22" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="W22" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.5</v>
-      </c>
-      <c r="X22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AI22" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.64</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.15</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,52 +3650,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.8</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>3.8</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="R23" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>1.98</v>
       </c>
       <c r="T23" t="n">
-        <v>1.53</v>
+        <v>1.77</v>
       </c>
       <c r="U23" t="n">
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="W23" t="n">
-        <v>4.2</v>
+        <v>6.5</v>
       </c>
       <c r="X23" t="n">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.05</v>
+        <v>1.9</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.24</v>
+        <v>1.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.94</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.4</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>4</v>
+        <v>6.7</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.62</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,83 +3932,83 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
         <v>2.95</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="S25" t="n">
         <v>2.05</v>
       </c>
-      <c r="O25" t="n">
-        <v>0</v>
-      </c>
-      <c r="P25" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="X25" t="n">
-        <v>1.63</v>
+        <v>1.4</v>
       </c>
       <c r="Y25" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI25" t="n">
         <v>2.3</v>
       </c>
-      <c r="Z25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE25" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI25" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>5.35</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.44</v>
+        <v>1.63</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O27" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="P27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.3</v>
+        <v>1.57</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>2.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.38</v>
+        <v>3.54</v>
       </c>
       <c r="T27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V27" t="n">
         <v>1.53</v>
       </c>
-      <c r="U27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.16</v>
-      </c>
       <c r="W27" t="n">
-        <v>4.1</v>
+        <v>2.5</v>
       </c>
       <c r="X27" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.5</v>
+        <v>4.65</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.42</v>
+        <v>1.12</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.57</v>
+        <v>2.04</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.35</v>
+        <v>1.46</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.69</v>
+        <v>1.48</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.38</v>
+        <v>1.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.6</v>
+        <v>3.64</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,46 +4496,46 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>3.72</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
         <v>0</v>
@@ -4544,10 +4544,10 @@
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4566,13 +4566,13 @@
         <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>5.75</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4737,27 +4737,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4878,27 +4878,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5010,7 +5010,7 @@
         <v>0</v>
       </c>
       <c r="AO32" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="33">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="35">
@@ -5301,27 +5301,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="36">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5498,43 +5498,43 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -5574,7 +5574,7 @@
         <v>0</v>
       </c>
       <c r="AO36" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="37">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,13 +5765,13 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="M38" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -5801,10 +5801,10 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Y38" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Z38" t="n">
         <v>0</v>
@@ -5856,7 +5856,7 @@
         <v>0</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="39">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,98 +5906,98 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.05</v>
+        <v>2.72</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="N39" t="n">
-        <v>3.4</v>
+        <v>2.44</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.39</v>
+        <v>1.3</v>
       </c>
       <c r="R39" t="n">
-        <v>2.68</v>
+        <v>3.25</v>
       </c>
       <c r="S39" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="T39" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="U39" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="V39" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W39" t="n">
-        <v>3.14</v>
+        <v>4.33</v>
       </c>
       <c r="X39" t="n">
-        <v>1.95</v>
+        <v>1.62</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z39" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AC39" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN39" t="n">
         <v>1.91</v>
       </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>4.16</v>
-      </c>
-      <c r="AK39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
       <c r="AO39" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="40">
@@ -6006,12 +6006,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,31 +6047,31 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>4.33</v>
+        <v>2.48</v>
       </c>
       <c r="M40" t="n">
-        <v>3.35</v>
+        <v>3.07</v>
       </c>
       <c r="N40" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -6083,47 +6083,47 @@
         <v>0</v>
       </c>
       <c r="X40" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI40" t="n">
         <v>2.2</v>
       </c>
-      <c r="Y40" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE40" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ40" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6132,13 +6132,13 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN40" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO40" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="41">
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,83 +6188,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="N41" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R41" t="n">
         <v>2.44</v>
       </c>
-      <c r="O41" t="n">
-        <v>2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.25</v>
-      </c>
       <c r="S41" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="U41" t="n">
         <v>1.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>4.33</v>
+        <v>2.56</v>
       </c>
       <c r="X41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.62</v>
       </c>
-      <c r="Y41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,58 +6329,58 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>3.34</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R42" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="U42" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="AA42" t="n">
         <v>1.14</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -6393,19 +6393,19 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>4.15</v>
+        <v>7.49</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN42" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,98 +6470,98 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>2</v>
-      </c>
       <c r="AN43" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="44">
@@ -6570,27 +6570,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,58 +6611,58 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="M44" t="n">
-        <v>3.41</v>
+        <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>6.3</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V44" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="W44" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="X44" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA44" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB44" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD44" t="inlineStr">
         <is>
@@ -6675,19 +6675,19 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI44" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6696,13 +6696,13 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO44" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="45">
@@ -6711,27 +6711,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,83 +6752,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>2.75</v>
       </c>
       <c r="M45" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>2.3</v>
       </c>
       <c r="O45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="R45" t="n">
-        <v>2.63</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W45" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="Y45" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
+      <c r="Z45" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.36</v>
       </c>
-      <c r="U45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W45" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA45" t="n">
+      <c r="AC45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
         <v>1.25</v>
       </c>
-      <c r="AB45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AG45" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="46">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,98 +6893,98 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="M46" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N46" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O46" t="n">
+        <v>3</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R46" t="n">
+        <v>3</v>
+      </c>
+      <c r="S46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W46" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z46" t="n">
         <v>3.3</v>
       </c>
-      <c r="N46" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O46" t="n">
+      <c r="AA46" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC46" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI46" t="n">
         <v>2.3</v>
       </c>
-      <c r="P46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="AJ46" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN46" t="n">
         <v>1.44</v>
       </c>
-      <c r="R46" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S46" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3</v>
-      </c>
-      <c r="X46" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AN46" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AO46" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="47">
@@ -6993,27 +6993,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,59 +7034,59 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="M47" t="n">
-        <v>4.3</v>
+        <v>2.75</v>
       </c>
       <c r="N47" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="R47" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="S47" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="V47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W47" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X47" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AC47" t="n">
         <v>1.55</v>
       </c>
-      <c r="O47" t="n">
-        <v>3</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="R47" t="n">
-        <v>3</v>
-      </c>
-      <c r="S47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U47" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V47" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W47" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X47" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Z47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>1.7</v>
-      </c>
       <c r="AD47" t="inlineStr">
         <is>
           <t>[]</t>
@@ -7098,19 +7098,19 @@
         </is>
       </c>
       <c r="AF47" t="n">
-        <v>2.55</v>
+        <v>1.22</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.11</v>
+        <v>1.55</v>
       </c>
       <c r="AH47" t="n">
-        <v>6.5</v>
+        <v>2.92</v>
       </c>
       <c r="AI47" t="n">
-        <v>2.3</v>
+        <v>1.84</v>
       </c>
       <c r="AJ47" t="n">
-        <v>2</v>
+        <v>5.08</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,13 +7175,13 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.75</v>
+        <v>2.18</v>
       </c>
       <c r="M48" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="N48" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="O48" t="n">
         <v>0</v>
@@ -7205,22 +7205,22 @@
         <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="X48" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y48" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z48" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AB48" t="n">
         <v>0</v>
@@ -7266,7 +7266,7 @@
         <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.15</v>
+        <v>2.45</v>
       </c>
       <c r="M49" t="n">
-        <v>2.75</v>
+        <v>2.95</v>
       </c>
       <c r="N49" t="n">
-        <v>3.95</v>
+        <v>2.95</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7331,43 +7331,43 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="W49" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="X49" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>5.08</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7407,7 +7407,7 @@
         <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.72916666666</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="50">
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,13 +7457,13 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="M50" t="n">
         <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.95</v>
+        <v>2.22</v>
       </c>
       <c r="O50" t="n">
         <v>0</v>
@@ -7487,16 +7487,16 @@
         <v>0</v>
       </c>
       <c r="V50" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -7548,7 +7548,7 @@
         <v>0</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="51">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,13 +7598,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.18</v>
+        <v>2.01</v>
       </c>
       <c r="M51" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7628,16 +7628,16 @@
         <v>0</v>
       </c>
       <c r="V51" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W51" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="X51" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z51" t="n">
         <v>0</v>
@@ -7689,7 +7689,7 @@
         <v>0</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.875</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,58 +7739,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V52" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W52" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X52" t="n">
-        <v>2.37</v>
+        <v>2.15</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7824,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.875</v>
       </c>
     </row>
     <row r="53">
@@ -7839,12 +7839,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.01</v>
+        <v>1.52</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="N53" t="n">
-        <v>3.55</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
         <v>0</v>
@@ -7910,16 +7910,16 @@
         <v>0</v>
       </c>
       <c r="V53" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>1.79</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>1.87</v>
       </c>
       <c r="Z53" t="n">
         <v>0</v>
@@ -7971,288 +7971,6 @@
         <v>0</v>
       </c>
       <c r="AO53" s="3" t="n">
-        <v>45887.875</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ecuador Primera Categoría Serie A</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Deportivo Cuenca</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>Cuniburo</t>
-        </is>
-      </c>
-      <c r="G54" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="n">
-        <v>0</v>
-      </c>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="n">
-        <v>0</v>
-      </c>
-      <c r="X54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE54" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="3" t="n">
-        <v>45887.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="n">
-        <v>0</v>
-      </c>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.45</v>
+        <v>3.28</v>
       </c>
       <c r="M2" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="N2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="Y2" t="n">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="Z2" t="n">
         <v>1.91</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,83 +2663,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.31</v>
+        <v>3.74</v>
       </c>
       <c r="M16" t="n">
-        <v>2.97</v>
+        <v>3.84</v>
       </c>
       <c r="N16" t="n">
-        <v>2.85</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="R16" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="W16" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF16" t="n">
         <v>1.95</v>
       </c>
-      <c r="P16" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R16" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="W16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="X16" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.4</v>
+        <v>2.43</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.05</v>
+        <v>1.62</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2945,58 +2945,58 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="inlineStr">
         <is>
@@ -3009,19 +3009,19 @@
         </is>
       </c>
       <c r="AF18" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
         <v>0</v>
@@ -3030,10 +3030,10 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
         <v>45887.5625</v>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45887.5625</v>
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,19 +3227,19 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.03</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
         <v>1.29</v>
@@ -3248,16 +3248,16 @@
         <v>3.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.45</v>
+        <v>2.34</v>
       </c>
       <c r="T20" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="U20" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W20" t="n">
         <v>4.33</v>
@@ -3269,41 +3269,41 @@
         <v>2.2</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.05</v>
+        <v>2.63</v>
       </c>
       <c r="AA20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AH20" t="n">
-        <v>2.3</v>
+        <v>2.61</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,83 +3368,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.75</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="R21" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.34</v>
+        <v>3.54</v>
       </c>
       <c r="T21" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V21" t="n">
         <v>1.53</v>
       </c>
-      <c r="U21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.17</v>
-      </c>
       <c r="W21" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.63</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.48</v>
       </c>
-      <c r="AB21" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.61</v>
+        <v>3.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.39</v>
+        <v>1.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.73</v>
+        <v>2.12</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>2.76</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>3.63</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.14</v>
+        <v>3.4</v>
       </c>
       <c r="S22" t="n">
-        <v>3.9</v>
+        <v>2.05</v>
       </c>
       <c r="T22" t="n">
-        <v>1.17</v>
+        <v>1.65</v>
       </c>
       <c r="U22" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="V22" t="n">
-        <v>1.63</v>
+        <v>1.13</v>
       </c>
       <c r="W22" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="X22" t="n">
-        <v>2.8</v>
+        <v>1.4</v>
       </c>
       <c r="Y22" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.4</v>
       </c>
-      <c r="Z22" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AC22" t="n">
-        <v>1.51</v>
+        <v>2.75</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH22" t="n">
-        <v>3</v>
+        <v>2.55</v>
       </c>
       <c r="AI22" t="n">
-        <v>1.93</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,52 +3650,52 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>2.26</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>3.21</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>2.73</v>
       </c>
       <c r="O23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
         <v>1.33</v>
       </c>
-      <c r="P23" t="n">
+      <c r="R23" t="n">
         <v>3.25</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="R23" t="n">
-        <v>4</v>
-      </c>
       <c r="S23" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="T23" t="n">
-        <v>1.77</v>
+        <v>1.44</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.25</v>
       </c>
       <c r="W23" t="n">
-        <v>6.5</v>
+        <v>3.85</v>
       </c>
       <c r="X23" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="Y23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3</v>
       </c>
-      <c r="Z23" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.4</v>
       </c>
       <c r="AB23" t="n">
         <v>1.62</v>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.5</v>
+        <v>1.57</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AJ23" t="n">
-        <v>6.7</v>
+        <v>3.25</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>1.83</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,95 +3791,95 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.26</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.21</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.73</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="R24" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="T24" t="n">
-        <v>1.44</v>
+        <v>1.54</v>
       </c>
       <c r="U24" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="V24" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="W24" t="n">
-        <v>3.85</v>
+        <v>4.33</v>
       </c>
       <c r="X24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.62</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AN24" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>2</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.03</v>
+        <v>2.95</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.41</v>
       </c>
       <c r="N25" t="n">
-        <v>2.95</v>
+        <v>2.05</v>
       </c>
       <c r="O25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,13 +4073,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>3.41</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
         <v>0</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.7</v>
+        <v>1.28</v>
       </c>
       <c r="M27" t="n">
-        <v>2.88</v>
+        <v>5.6</v>
       </c>
       <c r="N27" t="n">
-        <v>2.84</v>
+        <v>8.5</v>
       </c>
       <c r="O27" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="P27" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.57</v>
+        <v>1.2</v>
       </c>
       <c r="R27" t="n">
-        <v>2.36</v>
+        <v>4</v>
       </c>
       <c r="S27" t="n">
-        <v>3.54</v>
+        <v>1.98</v>
       </c>
       <c r="T27" t="n">
-        <v>1.25</v>
+        <v>1.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="V27" t="n">
-        <v>1.53</v>
+        <v>1.1</v>
       </c>
       <c r="W27" t="n">
-        <v>2.5</v>
+        <v>6.5</v>
       </c>
       <c r="X27" t="n">
-        <v>2.47</v>
+        <v>1.36</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.48</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.65</v>
+        <v>1.9</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.12</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.04</v>
+        <v>1.62</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.69</v>
+        <v>2.2</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.46</v>
+        <v>1.15</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.48</v>
+        <v>3.5</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.5</v>
+        <v>1.65</v>
       </c>
       <c r="AI27" t="n">
-        <v>1.9</v>
+        <v>2.75</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.64</v>
+        <v>6.7</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AN27" t="n">
-        <v>2.15</v>
+        <v>3.25</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4742,22 +4742,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -5024,22 +5024,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N36" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5498,43 +5498,43 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V36" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>3.14</v>
+        <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC36" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="AF36" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AJ36" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5639,43 +5639,43 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="X37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AH37" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AJ37" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5870,7 +5870,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,83 +5906,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="M39" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="N39" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O39" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P39" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.44</v>
       </c>
-      <c r="O39" t="n">
-        <v>2</v>
-      </c>
-      <c r="P39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R39" t="n">
-        <v>3.25</v>
-      </c>
       <c r="S39" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T39" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="U39" t="n">
         <v>1.04</v>
       </c>
       <c r="V39" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W39" t="n">
-        <v>4.33</v>
+        <v>2.56</v>
       </c>
       <c r="X39" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG39" t="n">
         <v>1.62</v>
       </c>
-      <c r="Y39" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH39" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AI39" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AJ39" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -5991,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO39" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,58 +6188,58 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M41" t="n">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="N41" t="n">
-        <v>3.34</v>
+        <v>6.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="R41" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="S41" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T41" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="U41" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="V41" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W41" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="X41" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Y41" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z41" t="n">
-        <v>4.35</v>
+        <v>4.7</v>
       </c>
       <c r="AA41" t="n">
         <v>1.14</v>
       </c>
       <c r="AB41" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AC41" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD41" t="inlineStr">
         <is>
@@ -6252,19 +6252,19 @@
         </is>
       </c>
       <c r="AF41" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="AG41" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AJ41" t="n">
-        <v>4.15</v>
+        <v>7.49</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AN41" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,59 +6329,59 @@
         </is>
       </c>
       <c r="L42" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M42" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N42" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O42" t="n">
+        <v>2</v>
+      </c>
+      <c r="P42" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R42" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S42" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V42" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W42" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X42" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA42" t="n">
         <v>1.5</v>
       </c>
-      <c r="M42" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N42" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R42" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S42" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W42" t="n">
+      <c r="AB42" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC42" t="n">
         <v>2.45</v>
       </c>
-      <c r="X42" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z42" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA42" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD42" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6393,31 +6393,31 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AI42" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
         <v>2</v>
       </c>
-      <c r="AJ42" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>0</v>
-      </c>
       <c r="AN42" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -7562,7 +7562,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,58 +7598,58 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="M51" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N51" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V51" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W51" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="X51" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA51" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC51" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
@@ -7662,19 +7662,19 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG51" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH51" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI51" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
@@ -7683,10 +7683,10 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN51" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO51" s="3" t="n">
         <v>45887.875</v>
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Athletic Club</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Criciúma</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,58 +7739,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>2.01</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N52" t="n">
-        <v>4.33</v>
+        <v>3.55</v>
       </c>
       <c r="O52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T52" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U52" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V52" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="X52" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH52" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI52" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AJ52" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AO52" s="3" t="n">
         <v>45887.875</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO53"/>
+  <dimension ref="A1:AO54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -789,7 +789,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -921,7 +921,7 @@
         <v>0</v>
       </c>
       <c r="AO3" s="3" t="n">
-        <v>45887.375</v>
+        <v>45887.35416666666</v>
       </c>
     </row>
     <row r="4">
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,58 +2240,58 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2304,19 +2304,19 @@
         </is>
       </c>
       <c r="AF13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.84</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.54166666666</v>
       </c>
     </row>
     <row r="19">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45887.5625</v>
@@ -3186,27 +3186,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.03</v>
+        <v>2.7</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="N20" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="R20" t="n">
-        <v>3.3</v>
+        <v>2.44</v>
       </c>
       <c r="S20" t="n">
-        <v>2.34</v>
+        <v>3.4</v>
       </c>
       <c r="T20" t="n">
-        <v>1.53</v>
+        <v>1.27</v>
       </c>
       <c r="U20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="V20" t="n">
-        <v>1.17</v>
+        <v>1.39</v>
       </c>
       <c r="W20" t="n">
-        <v>4.33</v>
+        <v>2.6</v>
       </c>
       <c r="X20" t="n">
-        <v>1.6</v>
+        <v>2.17</v>
       </c>
       <c r="Y20" t="n">
-        <v>2.2</v>
+        <v>1.62</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.63</v>
+        <v>4.45</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.48</v>
+        <v>1.14</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.47</v>
+        <v>1.99</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.3</v>
+        <v>1.75</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.67</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.61</v>
+        <v>4.04</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.39</v>
+        <v>1.94</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.5</v>
+        <v>3.01</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.73</v>
+        <v>2.31</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.1</v>
+        <v>1.83</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="21">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="O22" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="R22" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="T22" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="U22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V22" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="W22" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="X22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
         <v>2.05</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,31 +3573,31 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AI22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.26</v>
+        <v>2.95</v>
       </c>
       <c r="M23" t="n">
-        <v>3.21</v>
+        <v>3.41</v>
       </c>
       <c r="N23" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="O23" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="R23" t="n">
-        <v>3.25</v>
+        <v>3.28</v>
       </c>
       <c r="S23" t="n">
-        <v>2.63</v>
+        <v>2.28</v>
       </c>
       <c r="T23" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="U23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="V23" t="n">
-        <v>1.25</v>
+        <v>1.16</v>
       </c>
       <c r="W23" t="n">
-        <v>3.85</v>
+        <v>4.35</v>
       </c>
       <c r="X23" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Y23" t="n">
         <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.4</v>
+        <v>1.29</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.25</v>
+        <v>2.6</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.83</v>
+        <v>2.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,7 +3755,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,95 +3791,95 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>2.07</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>2.72</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>3.72</v>
       </c>
       <c r="O24" t="n">
-        <v>1.62</v>
+        <v>1.91</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.29</v>
+        <v>1.66</v>
       </c>
       <c r="R24" t="n">
-        <v>3.3</v>
+        <v>2.14</v>
       </c>
       <c r="S24" t="n">
-        <v>2.45</v>
+        <v>3.9</v>
       </c>
       <c r="T24" t="n">
-        <v>1.54</v>
+        <v>1.17</v>
       </c>
       <c r="U24" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="V24" t="n">
-        <v>1.18</v>
+        <v>1.57</v>
       </c>
       <c r="W24" t="n">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>5.3</v>
       </c>
       <c r="AA24" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.67</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG24" t="n">
+      <c r="AH24" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AH24" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AN24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,13 +3932,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.95</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.41</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.05</v>
+        <v>7.17</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3968,10 +3968,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
         <v>0</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="M28" t="n">
-        <v>2.76</v>
+        <v>3.75</v>
       </c>
       <c r="N28" t="n">
-        <v>3.63</v>
+        <v>3.1</v>
       </c>
       <c r="O28" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.66</v>
+        <v>1.29</v>
       </c>
       <c r="R28" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>3.9</v>
+        <v>2.34</v>
       </c>
       <c r="T28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V28" t="n">
         <v>1.17</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1.63</v>
-      </c>
       <c r="W28" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Y28" t="n">
         <v>2.2</v>
       </c>
-      <c r="X28" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.4</v>
-      </c>
       <c r="Z28" t="n">
-        <v>5.3</v>
+        <v>2.63</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>1.48</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>1.47</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.51</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.4</v>
+        <v>1.22</v>
       </c>
       <c r="AG28" t="n">
         <v>1.67</v>
       </c>
       <c r="AH28" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.93</v>
+        <v>2.39</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>4.65</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.64</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4737,27 +4737,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="32">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="35">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5433,7 +5433,7 @@
         <v>0</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="36">
@@ -5483,58 +5483,58 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>0</v>
+        <v>5.15</v>
       </c>
       <c r="M36" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S36" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W36" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="Y36" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA36" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AC36" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG36" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AJ36" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -5568,10 +5568,10 @@
         <v>0</v>
       </c>
       <c r="AM36" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AN36" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO36" s="3" t="n">
         <v>45887.625</v>
@@ -5633,31 +5633,31 @@
         <v>3.4</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
         <v>1.39</v>
       </c>
       <c r="R37" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="S37" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="U37" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="V37" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="X37" t="n">
         <v>1.95</v>
@@ -5666,16 +5666,16 @@
         <v>1.75</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.24</v>
+        <v>1.29</v>
       </c>
       <c r="AB37" t="n">
         <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
@@ -5688,10 +5688,10 @@
         </is>
       </c>
       <c r="AF37" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.63</v>
+        <v>1.73</v>
       </c>
       <c r="AH37" t="n">
         <v>2.7</v>
@@ -5709,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AO37" s="3" t="n">
         <v>45887.625</v>
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,58 +5765,58 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.33</v>
+        <v>2.1</v>
       </c>
       <c r="M38" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N38" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="O38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S38" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="X38" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="Y38" t="n">
-        <v>1.67</v>
+        <v>2.25</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5829,19 +5829,19 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AG38" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AH38" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ38" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -5850,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="39">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,55 +5906,55 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.12</v>
+        <v>4.33</v>
       </c>
       <c r="M39" t="n">
-        <v>3.14</v>
+        <v>3.35</v>
       </c>
       <c r="N39" t="n">
-        <v>3.34</v>
+        <v>1.69</v>
       </c>
       <c r="O39" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="P39" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="R39" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="S39" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="T39" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="U39" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="V39" t="n">
         <v>1.4</v>
       </c>
       <c r="W39" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="X39" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Z39" t="n">
-        <v>4.35</v>
+        <v>4.33</v>
       </c>
       <c r="AA39" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AB39" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="AC39" t="n">
         <v>1.7</v>
@@ -5970,19 +5970,19 @@
         </is>
       </c>
       <c r="AF39" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="AG39" t="n">
-        <v>1.62</v>
+        <v>1.2</v>
       </c>
       <c r="AH39" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="AI39" t="n">
-        <v>1.93</v>
+        <v>2.05</v>
       </c>
       <c r="AJ39" t="n">
-        <v>4.15</v>
+        <v>2.45</v>
       </c>
       <c r="AK39" t="n">
         <v>0</v>
@@ -5991,13 +5991,13 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>1.79</v>
+        <v>2.75</v>
       </c>
       <c r="AN39" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="AO39" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="40">
@@ -6152,22 +6152,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,59 +6188,59 @@
         </is>
       </c>
       <c r="L41" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N41" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="O41" t="n">
+        <v>2</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA41" t="n">
         <v>1.5</v>
       </c>
-      <c r="M41" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="N41" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0</v>
-      </c>
-      <c r="P41" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R41" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W41" t="n">
+      <c r="AB41" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC41" t="n">
         <v>2.45</v>
       </c>
-      <c r="X41" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AD41" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6252,31 +6252,31 @@
         </is>
       </c>
       <c r="AF41" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="AG41" t="n">
-        <v>2.24</v>
+        <v>1.45</v>
       </c>
       <c r="AH41" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AI41" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM41" t="n">
         <v>2</v>
       </c>
-      <c r="AJ41" t="n">
-        <v>7.49</v>
-      </c>
-      <c r="AK41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL41" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM41" t="n">
-        <v>0</v>
-      </c>
       <c r="AN41" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,95 +6329,95 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.72</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>2.44</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P42" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="R42" t="n">
-        <v>3.25</v>
+        <v>2.31</v>
       </c>
       <c r="S42" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>1.55</v>
+        <v>1.23</v>
       </c>
       <c r="U42" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF42" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG42" t="n">
         <v>2.25</v>
       </c>
-      <c r="Z42" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA42" t="n">
+      <c r="AH42" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM42" t="n">
         <v>1.5</v>
       </c>
-      <c r="AB42" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC42" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE42" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF42" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG42" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AH42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AI42" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ42" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL42" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM42" t="n">
-        <v>2</v>
-      </c>
       <c r="AN42" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,83 +6470,83 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.55</v>
+        <v>2.12</v>
       </c>
       <c r="M43" t="n">
-        <v>3.3</v>
+        <v>3.14</v>
       </c>
       <c r="N43" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O43" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P43" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W43" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH43" t="n">
         <v>2.8</v>
       </c>
-      <c r="O43" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="P43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S43" t="n">
-        <v>3</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U43" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V43" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="X43" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AI43" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AJ43" t="n">
-        <v>3.5</v>
+        <v>4.15</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -6555,13 +6555,13 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="44">
@@ -6711,27 +6711,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,58 +6752,58 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="M45" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q45" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>2.63</v>
       </c>
       <c r="S45" t="n">
-        <v>1.93</v>
+        <v>3</v>
       </c>
       <c r="T45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB45" t="n">
         <v>1.8</v>
       </c>
-      <c r="U45" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W45" t="n">
-        <v>6.18</v>
-      </c>
-      <c r="X45" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AC45" t="n">
-        <v>3</v>
+        <v>1.95</v>
       </c>
       <c r="AD45" t="inlineStr">
         <is>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="AF45" t="n">
-        <v>1.25</v>
+        <v>1.42</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH45" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="AI45" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>2.85</v>
+        <v>3.5</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -6837,13 +6837,13 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN45" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO45" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="46">
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,58 +7034,58 @@
         </is>
       </c>
       <c r="L47" t="n">
-        <v>2.15</v>
+        <v>2.75</v>
       </c>
       <c r="M47" t="n">
-        <v>2.75</v>
+        <v>3.95</v>
       </c>
       <c r="N47" t="n">
-        <v>3.95</v>
+        <v>2.3</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="R47" t="n">
-        <v>2.23</v>
+        <v>4</v>
       </c>
       <c r="S47" t="n">
-        <v>3.9</v>
+        <v>1.92</v>
       </c>
       <c r="T47" t="n">
-        <v>1.23</v>
+        <v>1.84</v>
       </c>
       <c r="U47" t="n">
-        <v>1.14</v>
+        <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.6</v>
+        <v>1.11</v>
       </c>
       <c r="W47" t="n">
-        <v>2.2</v>
+        <v>6.18</v>
       </c>
       <c r="X47" t="n">
-        <v>2.9</v>
+        <v>1.31</v>
       </c>
       <c r="Y47" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z47" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB47" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z47" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AA47" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AC47" t="n">
-        <v>1.55</v>
+        <v>3.1</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -7098,19 +7098,19 @@
         </is>
       </c>
       <c r="AF47" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.92</v>
+        <v>2.7</v>
       </c>
       <c r="AI47" t="n">
-        <v>1.84</v>
+        <v>2.46</v>
       </c>
       <c r="AJ47" t="n">
-        <v>5.08</v>
+        <v>3</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN47" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="48">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,58 +7175,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="M48" t="n">
-        <v>3.05</v>
+        <v>2.75</v>
       </c>
       <c r="N48" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="V48" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="W48" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="X48" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>0</v>
+        <v>5.92</v>
       </c>
       <c r="AA48" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AB48" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC48" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -7239,19 +7239,19 @@
         </is>
       </c>
       <c r="AF48" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG48" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH48" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AI48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AJ48" t="n">
-        <v>0</v>
+        <v>5.08</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -7260,13 +7260,13 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN48" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="49">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,58 +7316,58 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M49" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N49" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="V49" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W49" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="X49" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="Y49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7401,10 +7401,10 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO49" s="3" t="n">
         <v>45887.8125</v>
@@ -7416,12 +7416,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,58 +7457,58 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="M50" t="n">
         <v>2.95</v>
       </c>
       <c r="N50" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="O50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="V50" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W50" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="X50" t="n">
-        <v>2.37</v>
+        <v>2.55</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA50" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
@@ -7521,19 +7521,19 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -7542,13 +7542,13 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AO50" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="51">
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,58 +7598,58 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="M51" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>4.33</v>
+        <v>2.22</v>
       </c>
       <c r="O51" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="P51" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R51" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S51" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T51" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U51" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="V51" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W51" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X51" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z51" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB51" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC51" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD51" t="inlineStr">
         <is>
@@ -7662,19 +7662,19 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AG51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH51" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ51" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AK51" t="n">
         <v>0</v>
@@ -7683,13 +7683,13 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AN51" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="52">
@@ -7703,7 +7703,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Athletic Club</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Criciúma</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,58 +7739,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>3.55</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="S52" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T52" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="U52" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V52" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="W52" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="X52" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.4</v>
+        <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AG52" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI52" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7824,10 +7824,10 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AN52" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AO52" s="3" t="n">
         <v>45887.875</v>
@@ -7839,138 +7839,279 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Brazil Serie B</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Athletic Club</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Criciúma</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L53" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="M53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="N53" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="O53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="R53" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="S53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V53" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="X53" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE53" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF53" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AO53" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>23:00</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>USA NWSL</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>Seattle Reign</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>Chicago Red Stars</t>
         </is>
       </c>
-      <c r="G53" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" t="inlineStr">
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L53" t="n">
+      <c r="L54" t="n">
         <v>1.52</v>
       </c>
-      <c r="M53" t="n">
+      <c r="M54" t="n">
         <v>3.8</v>
       </c>
-      <c r="N53" t="n">
+      <c r="N54" t="n">
         <v>5</v>
       </c>
-      <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="P53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="n">
-        <v>0</v>
-      </c>
-      <c r="V53" t="n">
-        <v>0</v>
-      </c>
-      <c r="W53" t="n">
-        <v>0</v>
-      </c>
-      <c r="X53" t="n">
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W54" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X54" t="n">
         <v>1.79</v>
       </c>
-      <c r="Y53" t="n">
+      <c r="Y54" t="n">
         <v>1.87</v>
       </c>
-      <c r="Z53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE53" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO53" s="3" t="n">
+      <c r="Z54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC54" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF54" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG54" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>6</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO54" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.71</v>
+        <v>3.93</v>
       </c>
       <c r="N2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -725,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>1.83</v>
+        <v>1.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.87</v>
+        <v>3</v>
       </c>
       <c r="Z2" t="n">
         <v>1.91</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2522,31 +2522,31 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -2558,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
         <v>0</v>
@@ -2570,10 +2570,10 @@
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="inlineStr">
         <is>
@@ -2592,13 +2592,13 @@
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO15" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,7 +2768,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>2.88</v>
       </c>
       <c r="N22" t="n">
-        <v>3.8</v>
+        <v>2.84</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>2.12</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="R22" t="n">
-        <v>3.3</v>
+        <v>2.36</v>
       </c>
       <c r="S22" t="n">
-        <v>2.45</v>
+        <v>3.54</v>
       </c>
       <c r="T22" t="n">
-        <v>1.54</v>
+        <v>1.25</v>
       </c>
       <c r="U22" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="V22" t="n">
-        <v>1.18</v>
+        <v>1.53</v>
       </c>
       <c r="W22" t="n">
-        <v>4.33</v>
+        <v>2.5</v>
       </c>
       <c r="X22" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.05</v>
+        <v>4.65</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.25</v>
+        <v>1.69</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,31 +3573,31 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.29</v>
+        <v>1.46</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.91</v>
+        <v>1.48</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AI22" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AN22" t="n">
         <v>2.15</v>
-      </c>
-      <c r="AJ22" t="n">
-        <v>4</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM22" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>2.3</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.95</v>
+        <v>1.28</v>
       </c>
       <c r="M23" t="n">
-        <v>3.41</v>
+        <v>5.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.05</v>
+        <v>8.5</v>
       </c>
       <c r="O23" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="P23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R23" t="n">
+        <v>4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA23" t="n">
         <v>1.8</v>
       </c>
-      <c r="Q23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="R23" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W23" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.29</v>
+        <v>1.15</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>3.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.35</v>
+        <v>1.65</v>
       </c>
       <c r="AI23" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="AJ23" t="n">
-        <v>2.6</v>
+        <v>6.7</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="AN23" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,83 +3791,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.07</v>
+        <v>2.95</v>
       </c>
       <c r="M24" t="n">
-        <v>2.72</v>
+        <v>3.41</v>
       </c>
       <c r="N24" t="n">
-        <v>3.72</v>
+        <v>2.05</v>
       </c>
       <c r="O24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.66</v>
+        <v>1.25</v>
       </c>
       <c r="R24" t="n">
-        <v>2.14</v>
+        <v>3.28</v>
       </c>
       <c r="S24" t="n">
-        <v>3.9</v>
+        <v>2.28</v>
       </c>
       <c r="T24" t="n">
-        <v>1.17</v>
+        <v>1.53</v>
       </c>
       <c r="U24" t="n">
-        <v>1.14</v>
+        <v>1.03</v>
       </c>
       <c r="V24" t="n">
-        <v>1.57</v>
+        <v>1.16</v>
       </c>
       <c r="W24" t="n">
-        <v>2.15</v>
+        <v>4.35</v>
       </c>
       <c r="X24" t="n">
-        <v>2.9</v>
+        <v>1.63</v>
       </c>
       <c r="Y24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z24" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AH24" t="n">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.91</v>
+        <v>2.1</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>2.07</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>2.72</v>
       </c>
       <c r="N25" t="n">
-        <v>7.17</v>
+        <v>3.72</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.28</v>
+        <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>5.6</v>
+        <v>4</v>
       </c>
       <c r="N27" t="n">
-        <v>8.5</v>
+        <v>2.95</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="P27" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>3.4</v>
       </c>
       <c r="S27" t="n">
-        <v>1.98</v>
+        <v>2.05</v>
       </c>
       <c r="T27" t="n">
-        <v>1.77</v>
+        <v>1.65</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V27" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="X27" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="Y27" t="n">
-        <v>3</v>
+        <v>2.63</v>
       </c>
       <c r="Z27" t="n">
-        <v>1.9</v>
+        <v>2.05</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB27" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AN27" t="n">
-        <v>3.25</v>
+        <v>2</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N28" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="O28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.39</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>1.33</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21</v>
+        <v>5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.73</v>
+        <v>7.17</v>
       </c>
       <c r="O29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V29" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W29" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y29" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ29" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN29" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AN30" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="M31" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="N31" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="O31" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="R31" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="S31" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="T31" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="U31" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V31" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="X31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.63</v>
+        <v>2.2</v>
       </c>
       <c r="Z31" t="n">
         <v>2.05</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,31 +4842,31 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.65</v>
+        <v>1.91</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="AI31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN31" t="n">
         <v>2.3</v>
-      </c>
-      <c r="AJ31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AN31" t="n">
-        <v>2</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,83 +5624,83 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="M37" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="N37" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="O37" t="n">
         <v>1.73</v>
       </c>
       <c r="P37" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="R37" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="S37" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="T37" t="n">
-        <v>1.38</v>
+        <v>1.57</v>
       </c>
       <c r="U37" t="n">
         <v>1.03</v>
       </c>
       <c r="V37" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="W37" t="n">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="X37" t="n">
-        <v>1.95</v>
+        <v>1.6</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="Z37" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
         <v>1.29</v>
       </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AG37" t="n">
-        <v>1.73</v>
+        <v>1.6</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="AJ37" t="n">
-        <v>4.16</v>
+        <v>2.9</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>1.73</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AO37" s="3" t="n">
         <v>45887.625</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,58 +5765,58 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M38" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N38" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O38" t="n">
         <v>1.73</v>
       </c>
       <c r="P38" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="R38" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="S38" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="T38" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U38" t="n">
         <v>1.03</v>
       </c>
       <c r="V38" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W38" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="X38" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="Y38" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="Z38" t="n">
-        <v>2.45</v>
+        <v>3.3</v>
       </c>
       <c r="AA38" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AB38" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC38" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD38" t="inlineStr">
         <is>
@@ -5829,19 +5829,19 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AH38" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.9</v>
+        <v>4.16</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -5853,7 +5853,7 @@
         <v>1.73</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AO38" s="3" t="n">
         <v>45887.625</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,58 +6047,58 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.48</v>
+        <v>1.5</v>
       </c>
       <c r="M40" t="n">
-        <v>3.07</v>
+        <v>3.41</v>
       </c>
       <c r="N40" t="n">
-        <v>2.55</v>
+        <v>6.3</v>
       </c>
       <c r="O40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="P40" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="R40" t="n">
-        <v>2.75</v>
+        <v>2.31</v>
       </c>
       <c r="S40" t="n">
-        <v>2.75</v>
+        <v>3.5</v>
       </c>
       <c r="T40" t="n">
-        <v>1.4</v>
+        <v>1.23</v>
       </c>
       <c r="U40" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="X40" t="n">
-        <v>1.84</v>
+        <v>2.28</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.86</v>
+        <v>1.56</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA40" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.73</v>
+        <v>2.45</v>
       </c>
       <c r="AC40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -6111,19 +6111,19 @@
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG40" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH40" t="n">
-        <v>3.25</v>
+        <v>2.43</v>
       </c>
       <c r="AI40" t="n">
-        <v>2.2</v>
+        <v>1.77</v>
       </c>
       <c r="AJ40" t="n">
-        <v>3.1</v>
+        <v>7.49</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="AN40" t="n">
-        <v>1.91</v>
+        <v>3.5</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,58 +6329,58 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="N42" t="n">
-        <v>6.3</v>
+        <v>3.34</v>
       </c>
       <c r="O42" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="P42" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R42" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T42" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="V42" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W42" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="X42" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Z42" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -6393,19 +6393,19 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AG42" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AJ42" t="n">
-        <v>7.49</v>
+        <v>4.15</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AN42" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,58 +6470,58 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="M43" t="n">
-        <v>3.14</v>
+        <v>3.07</v>
       </c>
       <c r="N43" t="n">
-        <v>3.34</v>
+        <v>2.55</v>
       </c>
       <c r="O43" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="P43" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q43" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="R43" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="S43" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="T43" t="n">
-        <v>1.27</v>
+        <v>1.4</v>
       </c>
       <c r="U43" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W43" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>2.33</v>
+        <v>1.84</v>
       </c>
       <c r="Y43" t="n">
-        <v>1.54</v>
+        <v>1.86</v>
       </c>
       <c r="Z43" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="AA43" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB43" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AC43" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AD43" t="inlineStr">
         <is>
@@ -6534,19 +6534,19 @@
         </is>
       </c>
       <c r="AF43" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AG43" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AH43" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="AI43" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AJ43" t="n">
-        <v>4.15</v>
+        <v>3.1</v>
       </c>
       <c r="AK43" t="n">
         <v>0</v>
@@ -6555,10 +6555,10 @@
         <v>0</v>
       </c>
       <c r="AM43" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AN43" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AO43" s="3" t="n">
         <v>45887.64583333334</v>
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,58 +7316,58 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="M49" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="N49" t="n">
         <v>3.4</v>
       </c>
       <c r="O49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="T49" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U49" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="V49" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="W49" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="X49" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="Z49" t="n">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AA49" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AB49" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC49" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AI49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AJ49" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN49" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.79166666666</v>
       </c>
     </row>
     <row r="50">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,55 +7457,55 @@
         </is>
       </c>
       <c r="L50" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M50" t="n">
-        <v>2.95</v>
+        <v>3.05</v>
       </c>
       <c r="N50" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P50" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="R50" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="S50" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="T50" t="n">
         <v>1.29</v>
       </c>
       <c r="U50" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="V50" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="W50" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="X50" t="n">
-        <v>2.55</v>
+        <v>2.37</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AA50" t="n">
         <v>1.17</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="AC50" t="n">
         <v>1.65</v>
@@ -7521,19 +7521,19 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="AH50" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AJ50" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -7542,10 +7542,10 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="AO50" s="3" t="n">
         <v>45887.8125</v>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,84 +7598,84 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>3.03</v>
+        <v>2.45</v>
       </c>
       <c r="M51" t="n">
         <v>2.95</v>
       </c>
       <c r="N51" t="n">
-        <v>2.22</v>
+        <v>2.95</v>
       </c>
       <c r="O51" t="n">
+        <v>2</v>
+      </c>
+      <c r="P51" t="n">
         <v>2.25</v>
       </c>
-      <c r="P51" t="n">
+      <c r="Q51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="R51" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="S51" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI51" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH51" t="n">
+      <c r="AJ51" t="n">
         <v>3.75</v>
       </c>
-      <c r="AI51" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AK51" t="n">
         <v>0</v>
       </c>
@@ -7683,13 +7683,13 @@
         <v>0</v>
       </c>
       <c r="AM51" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN51" t="n">
         <v>2.25</v>
       </c>
-      <c r="AN51" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AO51" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,58 +7739,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>1.8</v>
+        <v>3.03</v>
       </c>
       <c r="M52" t="n">
-        <v>3.5</v>
+        <v>2.95</v>
       </c>
       <c r="N52" t="n">
-        <v>4.33</v>
+        <v>2.22</v>
       </c>
       <c r="O52" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="P52" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="R52" t="n">
-        <v>2.63</v>
+        <v>2.4</v>
       </c>
       <c r="S52" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T52" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="U52" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="V52" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="W52" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="X52" t="n">
-        <v>2.15</v>
+        <v>2.37</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.67</v>
+        <v>1.55</v>
       </c>
       <c r="Z52" t="n">
-        <v>3.8</v>
+        <v>4.15</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="AB52" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>1.2</v>
+        <v>1.35</v>
       </c>
       <c r="AG52" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH52" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI52" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH52" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI52" t="n">
-        <v>2.1</v>
-      </c>
       <c r="AJ52" t="n">
-        <v>5</v>
+        <v>2.9</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7824,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AN52" t="n">
-        <v>2.63</v>
+        <v>1.91</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45887.875</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="53">
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.01</v>
+        <v>2.34</v>
       </c>
       <c r="M53" t="n">
-        <v>2.95</v>
+        <v>3.04</v>
       </c>
       <c r="N53" t="n">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O53" t="n">
         <v>1.83</v>
@@ -7898,7 +7898,7 @@
         <v>1.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="S53" t="n">
         <v>3.4</v>
@@ -7907,31 +7907,31 @@
         <v>1.25</v>
       </c>
       <c r="U53" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="V53" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="W53" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="X53" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z53" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AA53" t="n">
         <v>1.15</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
@@ -7944,19 +7944,19 @@
         </is>
       </c>
       <c r="AF53" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="AG53" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH53" t="n">
-        <v>2.95</v>
+        <v>3.01</v>
       </c>
       <c r="AI53" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AJ53" t="n">
-        <v>3.4</v>
+        <v>4.47</v>
       </c>
       <c r="AK53" t="n">
         <v>0</v>
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Chicago Red Stars</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,58 +8021,58 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>1.52</v>
+        <v>1.8</v>
       </c>
       <c r="M54" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N54" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S54" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W54" t="n">
+        <v>3</v>
+      </c>
+      <c r="X54" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="Z54" t="n">
         <v>3.8</v>
       </c>
-      <c r="N54" t="n">
-        <v>5</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="P54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W54" t="n">
-        <v>3.48</v>
-      </c>
-      <c r="X54" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>2.9</v>
-      </c>
       <c r="AA54" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC54" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
@@ -8088,30 +8088,171 @@
         <v>1.2</v>
       </c>
       <c r="AG54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AH54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI54" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ54" t="n">
+        <v>5</v>
+      </c>
+      <c r="AK54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM54" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AO54" s="3" t="n">
+        <v>45887.875</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>45887</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Chicago Red Stars</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L55" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N55" t="n">
+        <v>5</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="S55" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V55" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W55" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X55" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="Y55" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Z55" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA55" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC55" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF55" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG55" t="n">
         <v>2.6</v>
       </c>
-      <c r="AH54" t="n">
+      <c r="AH55" t="n">
         <v>1.95</v>
       </c>
-      <c r="AI54" t="n">
+      <c r="AI55" t="n">
         <v>2.38</v>
       </c>
-      <c r="AJ54" t="n">
+      <c r="AJ55" t="n">
         <v>6</v>
       </c>
-      <c r="AK54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN54" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO54" s="3" t="n">
+      <c r="AK55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO55" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -689,13 +689,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.93</v>
+        <v>3.9</v>
       </c>
       <c r="N2" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="O2" t="n">
         <v>2.2</v>
@@ -704,43 +704,43 @@
         <v>1.62</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Y2" t="n">
         <v>3</v>
       </c>
       <c r="Z2" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AA2" t="n">
         <v>1.91</v>
       </c>
-      <c r="AA2" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AI2" t="n">
-        <v>2.63</v>
+        <v>2.72</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1227,12 +1227,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1253,58 +1253,58 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
@@ -1317,19 +1317,19 @@
         </is>
       </c>
       <c r="AF6" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
@@ -1338,10 +1338,10 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO6" s="3" t="n">
         <v>45887.5</v>
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45887.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,7 +1922,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1932,12 +1932,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2063,7 +2063,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2073,12 +2073,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,7 +2345,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zira</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Araz</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.47</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3.63</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2909,7 +2909,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Torpedo Moskva</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Ural</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -3086,58 +3086,58 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AD19" t="inlineStr">
         <is>
@@ -3150,19 +3150,19 @@
         </is>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AK19" t="n">
         <v>0</v>
@@ -3171,10 +3171,10 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AO19" s="3" t="n">
         <v>45887.5625</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Torpedo Moskva</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ural</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>4.45</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.5625</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="N21" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="O21" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="R21" t="n">
-        <v>3.25</v>
+        <v>2.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.63</v>
+        <v>3.54</v>
       </c>
       <c r="T21" t="n">
-        <v>1.44</v>
+        <v>1.25</v>
       </c>
       <c r="U21" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="V21" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="W21" t="n">
-        <v>3.85</v>
+        <v>2.5</v>
       </c>
       <c r="X21" t="n">
-        <v>1.62</v>
+        <v>2.35</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.3</v>
+        <v>1.52</v>
       </c>
       <c r="Z21" t="n">
-        <v>3</v>
+        <v>4.65</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.4</v>
+        <v>1.12</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>2.04</v>
       </c>
       <c r="AC21" t="n">
-        <v>2.2</v>
+        <v>1.69</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.57</v>
+        <v>1.48</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.25</v>
+        <v>3.64</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1.83</v>
+        <v>2.12</v>
       </c>
       <c r="AN21" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3473,22 +3473,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,83 +3509,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.7</v>
+        <v>2.03</v>
       </c>
       <c r="M22" t="n">
-        <v>2.88</v>
+        <v>4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="O22" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="R22" t="n">
-        <v>2.36</v>
+        <v>3.88</v>
       </c>
       <c r="S22" t="n">
-        <v>3.54</v>
+        <v>2.1</v>
       </c>
       <c r="T22" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W22" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF22" t="n">
         <v>1.25</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V22" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W22" t="n">
+      <c r="AG22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH22" t="n">
         <v>2.5</v>
       </c>
-      <c r="X22" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>3.5</v>
-      </c>
       <c r="AI22" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3.64</v>
+        <v>3</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>2.12</v>
+        <v>1.8</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3665,13 +3665,13 @@
         <v>3.25</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="R23" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="S23" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="T23" t="n">
         <v>1.77</v>
@@ -3680,13 +3680,13 @@
         <v>1.01</v>
       </c>
       <c r="V23" t="n">
-        <v>1.1</v>
+        <v>1.07</v>
       </c>
       <c r="W23" t="n">
-        <v>6.5</v>
+        <v>5.75</v>
       </c>
       <c r="X23" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="Y23" t="n">
         <v>3</v>
@@ -3701,7 +3701,7 @@
         <v>1.62</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,10 +3714,10 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="AG23" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AH23" t="n">
         <v>1.65</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,95 +3791,95 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.95</v>
+        <v>1.8</v>
       </c>
       <c r="M24" t="n">
-        <v>3.41</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.05</v>
+        <v>3.8</v>
       </c>
       <c r="O24" t="n">
-        <v>2.1</v>
+        <v>1.62</v>
       </c>
       <c r="P24" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="R24" t="n">
-        <v>3.28</v>
+        <v>3.1</v>
       </c>
       <c r="S24" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T24" t="n">
         <v>1.53</v>
       </c>
       <c r="U24" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W24" t="n">
-        <v>4.35</v>
+        <v>4.6</v>
       </c>
       <c r="X24" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="Y24" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>4</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AN24" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE24" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ24" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AK24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM24" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AN24" t="n">
-        <v>1.8</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,7 +3896,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.07</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>3.72</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,58 +4073,58 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>3.04</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="O26" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="R26" t="n">
         <v>3.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="T26" t="n">
         <v>1.53</v>
       </c>
       <c r="U26" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="V26" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W26" t="n">
         <v>4.33</v>
       </c>
       <c r="X26" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="Y26" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="AD26" t="inlineStr">
         <is>
@@ -4137,19 +4137,19 @@
         </is>
       </c>
       <c r="AF26" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="AI26" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3.5</v>
+        <v>2.64</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.73</v>
+        <v>2.1</v>
       </c>
       <c r="AN26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4217,55 +4217,55 @@
         <v>2.03</v>
       </c>
       <c r="M27" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="N27" t="n">
-        <v>2.95</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R27" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="S27" t="n">
-        <v>2.05</v>
+        <v>2.36</v>
       </c>
       <c r="T27" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V27" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="W27" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="X27" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="Y27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Z27" t="n">
         <v>2.63</v>
       </c>
-      <c r="Z27" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA27" t="n">
-        <v>1.68</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.4</v>
+        <v>1.58</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.75</v>
+        <v>2.29</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AJ27" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AN27" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>3.72</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,13 +4496,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>7.17</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4752,12 +4752,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,83 +4778,83 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.8</v>
+        <v>3.21</v>
       </c>
       <c r="N31" t="n">
-        <v>3.8</v>
+        <v>2.73</v>
       </c>
       <c r="O31" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X31" t="n">
         <v>1.62</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Y31" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="R31" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W31" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Y31" t="n">
+      <c r="Z31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.2</v>
       </c>
-      <c r="Z31" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC31" t="n">
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2.25</v>
       </c>
-      <c r="AD31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF31" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,10 +4863,10 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AN31" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AO31" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5165,22 +5165,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,95 +5483,95 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>5.15</v>
+        <v>2.1</v>
       </c>
       <c r="M36" t="n">
-        <v>4.15</v>
+        <v>3.4</v>
       </c>
       <c r="N36" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="O36" t="n">
-        <v>2.63</v>
+        <v>1.73</v>
       </c>
       <c r="P36" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="R36" t="n">
-        <v>3.28</v>
+        <v>3.15</v>
       </c>
       <c r="S36" t="n">
         <v>2.25</v>
       </c>
       <c r="T36" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="U36" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="V36" t="n">
-        <v>1.19</v>
+        <v>1.12</v>
       </c>
       <c r="W36" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="X36" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="Y36" t="n">
         <v>2.2</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="AB36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF36" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG36" t="n">
         <v>1.65</v>
       </c>
-      <c r="AC36" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AD36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF36" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AH36" t="n">
-        <v>4.75</v>
+        <v>2.65</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="AJ36" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AN36" t="n">
         <v>2.1</v>
-      </c>
-      <c r="AK36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AN36" t="n">
-        <v>1.5</v>
       </c>
       <c r="AO36" s="3" t="n">
         <v>45887.625</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,58 +5624,58 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M37" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="O37" t="n">
         <v>1.73</v>
       </c>
       <c r="P37" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q37" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="R37" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="S37" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="T37" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="U37" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="V37" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="W37" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="X37" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="Y37" t="n">
-        <v>2.25</v>
+        <v>1.76</v>
       </c>
       <c r="Z37" t="n">
-        <v>2.45</v>
+        <v>3.34</v>
       </c>
       <c r="AA37" t="n">
-        <v>1.5</v>
+        <v>1.24</v>
       </c>
       <c r="AB37" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AC37" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="AD37" t="inlineStr">
         <is>
@@ -5688,19 +5688,19 @@
         </is>
       </c>
       <c r="AF37" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AG37" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH37" t="n">
-        <v>2.55</v>
+        <v>2.69</v>
       </c>
       <c r="AI37" t="n">
-        <v>2.5</v>
+        <v>2.02</v>
       </c>
       <c r="AJ37" t="n">
-        <v>2.9</v>
+        <v>4.16</v>
       </c>
       <c r="AK37" t="n">
         <v>0</v>
@@ -5712,7 +5712,7 @@
         <v>1.73</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AO37" s="3" t="n">
         <v>45887.625</v>
@@ -5729,7 +5729,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,84 +5765,84 @@
         </is>
       </c>
       <c r="L38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M38" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N38" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R38" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S38" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W38" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.05</v>
       </c>
-      <c r="M38" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P38" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S38" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4.16</v>
-      </c>
       <c r="AK38" t="n">
         <v>0</v>
       </c>
@@ -5850,10 +5850,10 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AN38" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO38" s="3" t="n">
         <v>45887.625</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>4.33</v>
+        <v>5</v>
       </c>
       <c r="M39" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="N39" t="n">
         <v>1.69</v>
@@ -5942,10 +5942,10 @@
         <v>2.7</v>
       </c>
       <c r="X39" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Y39" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="Z39" t="n">
         <v>4.33</v>
@@ -6011,22 +6011,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Defensores de Belgrano</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Defensores Unidos</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,58 +6047,58 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>1.5</v>
+        <v>2.12</v>
       </c>
       <c r="M40" t="n">
-        <v>3.41</v>
+        <v>3.14</v>
       </c>
       <c r="N40" t="n">
-        <v>6.3</v>
+        <v>3.34</v>
       </c>
       <c r="O40" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="P40" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="R40" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="S40" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="T40" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="U40" t="n">
-        <v>1.11</v>
+        <v>1.04</v>
       </c>
       <c r="V40" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="W40" t="n">
-        <v>2.45</v>
+        <v>2.56</v>
       </c>
       <c r="X40" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="Z40" t="n">
-        <v>5</v>
+        <v>4.35</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AB40" t="n">
-        <v>2.45</v>
+        <v>1.98</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -6111,19 +6111,19 @@
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="AG40" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.43</v>
+        <v>2.8</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.77</v>
+        <v>1.93</v>
       </c>
       <c r="AJ40" t="n">
-        <v>7.49</v>
+        <v>4.15</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.5</v>
+        <v>1.79</v>
       </c>
       <c r="AN40" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6293,22 +6293,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Defensores de Belgrano</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Defensores Unidos</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6329,58 +6329,58 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.14</v>
+        <v>3.41</v>
       </c>
       <c r="N42" t="n">
-        <v>3.34</v>
+        <v>6.3</v>
       </c>
       <c r="O42" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="R42" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="S42" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
         <v>1.27</v>
       </c>
       <c r="U42" t="n">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="V42" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>2.56</v>
+        <v>2.45</v>
       </c>
       <c r="X42" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="Z42" t="n">
-        <v>4.35</v>
+        <v>4.92</v>
       </c>
       <c r="AA42" t="n">
         <v>1.14</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.98</v>
+        <v>2.5</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AD42" t="inlineStr">
         <is>
@@ -6393,19 +6393,19 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>1.27</v>
+        <v>1.07</v>
       </c>
       <c r="AG42" t="n">
-        <v>1.62</v>
+        <v>2.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AJ42" t="n">
-        <v>4.15</v>
+        <v>7.49</v>
       </c>
       <c r="AK42" t="n">
         <v>0</v>
@@ -6414,10 +6414,10 @@
         <v>0</v>
       </c>
       <c r="AM42" t="n">
-        <v>1.79</v>
+        <v>1.5</v>
       </c>
       <c r="AN42" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AO42" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,19 +6611,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>3.5</v>
+        <v>2.55</v>
       </c>
       <c r="M44" t="n">
         <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="O44" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="P44" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="Q44" t="n">
         <v>1.44</v>
@@ -6632,38 +6632,38 @@
         <v>2.63</v>
       </c>
       <c r="S44" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="T44" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="U44" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="V44" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="W44" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="X44" t="n">
-        <v>2.2</v>
+        <v>2.05</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="AA44" t="n">
         <v>1.25</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AD44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6675,19 +6675,19 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>1.65</v>
+        <v>1.42</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AH44" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="AI44" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>2.88</v>
+        <v>3.5</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="AN44" t="n">
-        <v>1.8</v>
+        <v>2.05</v>
       </c>
       <c r="AO44" s="3" t="n">
         <v>45887.66666666666</v>
@@ -6716,7 +6716,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,19 +6752,19 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="M45" t="n">
         <v>3.3</v>
       </c>
       <c r="N45" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O45" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P45" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q45" t="n">
         <v>1.44</v>
@@ -6773,38 +6773,38 @@
         <v>2.63</v>
       </c>
       <c r="S45" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W45" t="n">
         <v>3</v>
       </c>
-      <c r="T45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W45" t="n">
-        <v>3.1</v>
-      </c>
       <c r="X45" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Y45" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z45" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA45" t="n">
         <v>1.25</v>
       </c>
       <c r="AB45" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC45" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC45" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD45" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6816,19 +6816,19 @@
         </is>
       </c>
       <c r="AF45" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG45" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH45" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AI45" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ45" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK45" t="n">
         <v>0</v>
@@ -6837,10 +6837,10 @@
         <v>0</v>
       </c>
       <c r="AM45" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AN45" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AO45" s="3" t="n">
         <v>45887.66666666666</v>
@@ -7049,16 +7049,16 @@
         <v>1.91</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="R47" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="S47" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="T47" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="U47" t="n">
         <v>1.01</v>
@@ -7070,7 +7070,7 @@
         <v>6.18</v>
       </c>
       <c r="X47" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="Y47" t="n">
         <v>3</v>
@@ -7085,7 +7085,7 @@
         <v>1.36</v>
       </c>
       <c r="AC47" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="AD47" t="inlineStr">
         <is>
@@ -7101,10 +7101,10 @@
         <v>1.25</v>
       </c>
       <c r="AG47" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="AI47" t="n">
         <v>2.46</v>
@@ -7190,19 +7190,19 @@
         <v>2.75</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="R48" t="n">
-        <v>2.09</v>
+        <v>2.3</v>
       </c>
       <c r="S48" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T48" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="U48" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="V48" t="n">
         <v>1.6</v>
@@ -7217,16 +7217,16 @@
         <v>1.36</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.92</v>
+        <v>5.6</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -7242,13 +7242,13 @@
         <v>1.22</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.73</v>
+        <v>1.88</v>
       </c>
       <c r="AJ48" t="n">
         <v>5.08</v>
@@ -7316,13 +7316,13 @@
         </is>
       </c>
       <c r="L49" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="M49" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="N49" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O49" t="n">
         <v>0</v>
@@ -7331,43 +7331,43 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="S49" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T49" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="U49" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="V49" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="W49" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="X49" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="Y49" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="Z49" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA49" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB49" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AC49" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AG49" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH49" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AI49" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AJ49" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7472,19 +7472,19 @@
         <v>2.5</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R50" t="n">
-        <v>2.4</v>
+        <v>2.22</v>
       </c>
       <c r="S50" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="T50" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="U50" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="V50" t="n">
         <v>1.55</v>
@@ -7499,16 +7499,16 @@
         <v>1.48</v>
       </c>
       <c r="Z50" t="n">
-        <v>5.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="AC50" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="AD50" t="inlineStr">
         <is>
@@ -7521,19 +7521,19 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AJ50" t="n">
-        <v>4.2</v>
+        <v>4.25</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -7613,19 +7613,19 @@
         <v>2.25</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="R51" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="S51" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="T51" t="n">
-        <v>1.29</v>
+        <v>1.18</v>
       </c>
       <c r="U51" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="V51" t="n">
         <v>1.5</v>
@@ -7637,16 +7637,16 @@
         <v>2.55</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="Z51" t="n">
         <v>5</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="AB51" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AC51" t="n">
         <v>1.65</v>
@@ -7662,16 +7662,16 @@
         </is>
       </c>
       <c r="AF51" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AG51" t="n">
-        <v>1.53</v>
+        <v>1.41</v>
       </c>
       <c r="AH51" t="n">
-        <v>3.2</v>
+        <v>3.38</v>
       </c>
       <c r="AI51" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AJ51" t="n">
         <v>3.75</v>
@@ -7754,10 +7754,10 @@
         <v>1.91</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R52" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="S52" t="n">
         <v>3.2</v>
@@ -7766,31 +7766,31 @@
         <v>1.3</v>
       </c>
       <c r="U52" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="V52" t="n">
         <v>1.4</v>
       </c>
       <c r="W52" t="n">
-        <v>2.75</v>
+        <v>2.7</v>
       </c>
       <c r="X52" t="n">
-        <v>2.37</v>
+        <v>2.07</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.15</v>
+        <v>4.2</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AG52" t="n">
         <v>1.36</v>
@@ -7812,10 +7812,10 @@
         <v>3.75</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7880,13 +7880,13 @@
         </is>
       </c>
       <c r="L53" t="n">
-        <v>2.34</v>
+        <v>2.07</v>
       </c>
       <c r="M53" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="N53" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="O53" t="n">
         <v>1.83</v>
@@ -7898,7 +7898,7 @@
         <v>1.55</v>
       </c>
       <c r="R53" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="S53" t="n">
         <v>3.4</v>
@@ -7913,10 +7913,10 @@
         <v>1.51</v>
       </c>
       <c r="W53" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="X53" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Y53" t="n">
         <v>1.5</v>
@@ -7928,10 +7928,10 @@
         <v>1.15</v>
       </c>
       <c r="AB53" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AC53" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AD53" t="inlineStr">
         <is>
@@ -7944,19 +7944,19 @@
         </is>
       </c>
       <c r="AF53" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="AG53" t="n">
         <v>1.66</v>
       </c>
       <c r="AH53" t="n">
-        <v>3.01</v>
+        <v>2.93</v>
       </c>
       <c r="AI53" t="n">
         <v>1.91</v>
       </c>
       <c r="AJ53" t="n">
-        <v>4.47</v>
+        <v>4.1</v>
       </c>
       <c r="AK53" t="n">
         <v>0</v>
@@ -8180,22 +8180,22 @@
         <v>1.33</v>
       </c>
       <c r="R55" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="S55" t="n">
-        <v>2.58</v>
+        <v>2.5</v>
       </c>
       <c r="T55" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="U55" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V55" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="W55" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="X55" t="n">
         <v>1.79</v>
@@ -8238,7 +8238,7 @@
         <v>2.38</v>
       </c>
       <c r="AJ55" t="n">
-        <v>6</v>
+        <v>6.16</v>
       </c>
       <c r="AK55" t="n">
         <v>0</v>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO55"/>
+  <dimension ref="A1:AO54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>5.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2099,58 +2099,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="inlineStr">
         <is>
@@ -2163,19 +2163,19 @@
         </is>
       </c>
       <c r="AF12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
@@ -2184,10 +2184,10 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO12" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Mes Rafsanjan</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2240,31 +2240,31 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.61</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>0</v>
@@ -2288,10 +2288,10 @@
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="inlineStr">
         <is>
@@ -2310,13 +2310,13 @@
         <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
@@ -2325,10 +2325,10 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AO13" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Zira</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Araz</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,58 +2381,58 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD14" t="inlineStr">
         <is>
@@ -2445,19 +2445,19 @@
         </is>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mes Rafsanjan</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2637,12 +2637,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2768,22 +2768,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2804,31 +2804,31 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z17" t="n">
         <v>0</v>
@@ -2852,10 +2852,10 @@
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AD17" t="inlineStr">
         <is>
@@ -2874,13 +2874,13 @@
         <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AK17" t="n">
         <v>0</v>
@@ -2889,10 +2889,10 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AO17" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Al-Rustaq</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Sohar</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3036,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="AO18" s="3" t="n">
-        <v>45887.54166666666</v>
+        <v>45887.5625</v>
       </c>
     </row>
     <row r="19">
@@ -3186,27 +3186,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al-Rustaq</t>
+          <t>Agropecuario</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sohar</t>
+          <t>Club Atlético Mitre</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,58 +3227,58 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.63</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AD20" t="inlineStr">
         <is>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,13 +3312,13 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO20" s="3" t="n">
-        <v>45887.5625</v>
+        <v>45887.58333333334</v>
       </c>
     </row>
     <row r="21">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3342,12 +3342,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
-        <v>3.64</v>
+        <v>0</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,58 +3509,58 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="M22" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N22" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O22" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.88</v>
+        <v>3.2</v>
       </c>
       <c r="S22" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
       <c r="T22" t="n">
-        <v>1.77</v>
+        <v>1.5</v>
       </c>
       <c r="U22" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="V22" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>5.5</v>
+        <v>3.98</v>
       </c>
       <c r="X22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA22" t="n">
         <v>1.4</v>
       </c>
-      <c r="Y22" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.68</v>
-      </c>
       <c r="AB22" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.75</v>
+        <v>2.15</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3576,16 +3576,16 @@
         <v>1.25</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AN22" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,22 +3614,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,83 +3650,83 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.28</v>
+        <v>2.7</v>
       </c>
       <c r="M23" t="n">
-        <v>5.6</v>
+        <v>2.88</v>
       </c>
       <c r="N23" t="n">
-        <v>8.5</v>
+        <v>2.84</v>
       </c>
       <c r="O23" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="P23" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.16</v>
+        <v>1.57</v>
       </c>
       <c r="R23" t="n">
-        <v>4.3</v>
+        <v>2.36</v>
       </c>
       <c r="S23" t="n">
-        <v>2.02</v>
+        <v>3.54</v>
       </c>
       <c r="T23" t="n">
-        <v>1.77</v>
+        <v>1.25</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="V23" t="n">
-        <v>1.07</v>
+        <v>1.53</v>
       </c>
       <c r="W23" t="n">
-        <v>5.75</v>
+        <v>2.5</v>
       </c>
       <c r="X23" t="n">
-        <v>1.34</v>
+        <v>2.35</v>
       </c>
       <c r="Y23" t="n">
-        <v>3</v>
+        <v>1.52</v>
       </c>
       <c r="Z23" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AI23" t="n">
         <v>1.9</v>
       </c>
-      <c r="AA23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AI23" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AJ23" t="n">
-        <v>6.7</v>
+        <v>3.64</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>1.33</v>
+        <v>2.12</v>
       </c>
       <c r="AN23" t="n">
-        <v>3.25</v>
+        <v>2.15</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group D</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>3.04</v>
       </c>
       <c r="M25" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="N25" t="n">
-        <v>7</v>
+        <v>2.18</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4037,22 +4037,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.04</v>
+        <v>2.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.18</v>
+        <v>2.95</v>
       </c>
       <c r="O26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="P26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="n">
         <v>1.25</v>
       </c>
       <c r="R26" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="S26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="W26" t="n">
+        <v>5</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AI26" t="n">
         <v>2.3</v>
       </c>
-      <c r="T26" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>2.29</v>
-      </c>
       <c r="AJ26" t="n">
-        <v>2.64</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="AN26" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4188,12 +4188,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,95 +4214,95 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.03</v>
+        <v>1.22</v>
       </c>
       <c r="M27" t="n">
-        <v>3.75</v>
+        <v>5.2</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="O27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="P27" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="T27" t="n">
         <v>1.73</v>
       </c>
-      <c r="P27" t="n">
+      <c r="U27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q27" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W27" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="X27" t="n">
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.6</v>
       </c>
-      <c r="Y27" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AD27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AI27" t="n">
-        <v>2.39</v>
+        <v>2.75</v>
       </c>
       <c r="AJ27" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN27" t="n">
         <v>3.25</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>2.1</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,7 +4319,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -4329,12 +4329,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.07</v>
+        <v>1.33</v>
       </c>
       <c r="M28" t="n">
-        <v>2.72</v>
+        <v>5</v>
       </c>
       <c r="N28" t="n">
-        <v>3.72</v>
+        <v>7</v>
       </c>
       <c r="O28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>4.25</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="U28" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>4.82</v>
+        <v>0</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AN28" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD29" t="inlineStr">
         <is>
@@ -4560,19 +4560,19 @@
         </is>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK29" t="n">
         <v>0</v>
@@ -4581,10 +4581,10 @@
         <v>0</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO29" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4601,22 +4601,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4637,58 +4637,58 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="inlineStr">
         <is>
@@ -4701,19 +4701,19 @@
         </is>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AK30" t="n">
         <v>0</v>
@@ -4722,10 +4722,10 @@
         <v>0</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4737,27 +4737,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Luxembourg National Division</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Differdange 03</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Racing</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4778,58 +4778,58 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="X31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Y31" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="inlineStr">
         <is>
@@ -4842,19 +4842,19 @@
         </is>
       </c>
       <c r="AF31" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AK31" t="n">
         <v>0</v>
@@ -4863,13 +4863,13 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AO31" s="3" t="n">
-        <v>45887.58333333334</v>
+        <v>45887.60416666666</v>
       </c>
     </row>
     <row r="32">
@@ -4883,22 +4883,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Luxembourg National Division</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Differdange 03</t>
+          <t>B36</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Racing</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -5034,12 +5034,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>B36</t>
+          <t>Víkingur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>NSÍ</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -5160,27 +5160,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Víkingur</t>
+          <t>Al Jazeera</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>NSÍ</t>
+          <t>Sama Al Sarhan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5292,7 +5292,7 @@
         <v>0</v>
       </c>
       <c r="AO34" s="3" t="n">
-        <v>45887.60416666666</v>
+        <v>45887.61458333334</v>
       </c>
     </row>
     <row r="35">
@@ -5301,12 +5301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Al Jazeera</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Sama Al Sarhan</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -5342,58 +5342,58 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA35" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AD35" t="inlineStr">
         <is>
@@ -5406,19 +5406,19 @@
         </is>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ35" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AK35" t="n">
         <v>0</v>
@@ -5427,13 +5427,13 @@
         <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO35" s="3" t="n">
-        <v>45887.61458333334</v>
+        <v>45887.625</v>
       </c>
     </row>
     <row r="36">
@@ -5447,7 +5447,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB II</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5457,12 +5457,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Kecskeméti TE</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Videoton</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -5483,58 +5483,58 @@
         </is>
       </c>
       <c r="L36" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="M36" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="N36" t="n">
         <v>3.4</v>
-      </c>
-      <c r="N36" t="n">
-        <v>2.8</v>
       </c>
       <c r="O36" t="n">
         <v>1.73</v>
       </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="Q36" t="n">
-        <v>1.27</v>
+        <v>1.39</v>
       </c>
       <c r="R36" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="S36" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="T36" t="n">
-        <v>1.58</v>
+        <v>1.38</v>
       </c>
       <c r="U36" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="V36" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="W36" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="X36" t="n">
-        <v>1.65</v>
+        <v>1.94</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.2</v>
+        <v>1.76</v>
       </c>
       <c r="Z36" t="n">
-        <v>2.8</v>
+        <v>3.34</v>
       </c>
       <c r="AA36" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AB36" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC36" t="n">
-        <v>2.2</v>
+        <v>1.95</v>
       </c>
       <c r="AD36" t="inlineStr">
         <is>
@@ -5547,19 +5547,19 @@
         </is>
       </c>
       <c r="AF36" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AG36" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="AH36" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="AI36" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="AJ36" t="n">
-        <v>3.4</v>
+        <v>4.16</v>
       </c>
       <c r="AK36" t="n">
         <v>0</v>
@@ -5571,7 +5571,7 @@
         <v>1.73</v>
       </c>
       <c r="AN36" t="n">
-        <v>2.1</v>
+        <v>2.33</v>
       </c>
       <c r="AO36" s="3" t="n">
         <v>45887.625</v>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hungary NB II</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -5598,12 +5598,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kecskeméti TE</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Videoton</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -5624,84 +5624,84 @@
         </is>
       </c>
       <c r="L37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M37" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="N37" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="O37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="R37" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="S37" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W37" t="n">
+        <v>4.12</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF37" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ37" t="n">
         <v>2.05</v>
       </c>
-      <c r="M37" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="N37" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O37" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="P37" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="Q37" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="R37" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="S37" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T37" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="U37" t="n">
-        <v>1</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W37" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="X37" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="Y37" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="Z37" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AA37" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AB37" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC37" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE37" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF37" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG37" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="AH37" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="AI37" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>4.16</v>
-      </c>
       <c r="AK37" t="n">
         <v>0</v>
       </c>
@@ -5709,10 +5709,10 @@
         <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1.73</v>
+        <v>2.63</v>
       </c>
       <c r="AN37" t="n">
-        <v>2.33</v>
+        <v>1.5</v>
       </c>
       <c r="AO37" s="3" t="n">
         <v>45887.625</v>
@@ -5724,12 +5724,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Arda</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -5765,59 +5765,59 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="M38" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="N38" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="O38" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P38" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.31</v>
+        <v>1.44</v>
       </c>
       <c r="R38" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="S38" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="T38" t="n">
-        <v>1.48</v>
+        <v>1.33</v>
       </c>
       <c r="U38" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="V38" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="W38" t="n">
-        <v>4.12</v>
+        <v>2.7</v>
       </c>
       <c r="X38" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC38" t="n">
         <v>1.7</v>
       </c>
-      <c r="Y38" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AD38" t="inlineStr">
         <is>
           <t>[]</t>
@@ -5829,19 +5829,19 @@
         </is>
       </c>
       <c r="AF38" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AG38" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="AH38" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AI38" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AJ38" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AK38" t="n">
         <v>0</v>
@@ -5850,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="AN38" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AO38" s="3" t="n">
-        <v>45887.625</v>
+        <v>45887.63541666666</v>
       </c>
     </row>
     <row r="39">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -5880,12 +5880,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Arda</t>
+          <t>SSC Farul</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Universitatea Cluj</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -5906,84 +5906,84 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>5</v>
+        <v>2.48</v>
       </c>
       <c r="M39" t="n">
-        <v>3.4</v>
+        <v>3.07</v>
       </c>
       <c r="N39" t="n">
-        <v>1.69</v>
+        <v>2.55</v>
       </c>
       <c r="O39" t="n">
+        <v>2</v>
+      </c>
+      <c r="P39" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="R39" t="n">
         <v>2.75</v>
       </c>
-      <c r="P39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R39" t="n">
-        <v>2.62</v>
-      </c>
       <c r="S39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AJ39" t="n">
         <v>3.1</v>
       </c>
-      <c r="T39" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U39" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="W39" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="X39" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AA39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AK39" t="n">
         <v>0</v>
       </c>
@@ -5991,13 +5991,13 @@
         <v>0</v>
       </c>
       <c r="AM39" t="n">
-        <v>2.75</v>
+        <v>2</v>
       </c>
       <c r="AN39" t="n">
-        <v>1.57</v>
+        <v>1.91</v>
       </c>
       <c r="AO39" s="3" t="n">
-        <v>45887.63541666666</v>
+        <v>45887.64583333334</v>
       </c>
     </row>
     <row r="40">
@@ -6011,7 +6011,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -6021,12 +6021,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>BB Erzurumspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -6047,58 +6047,58 @@
         </is>
       </c>
       <c r="L40" t="n">
-        <v>2.12</v>
+        <v>2.72</v>
       </c>
       <c r="M40" t="n">
-        <v>3.14</v>
+        <v>3.52</v>
       </c>
       <c r="N40" t="n">
-        <v>3.34</v>
+        <v>2.44</v>
       </c>
       <c r="O40" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="R40" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="S40" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="T40" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="U40" t="n">
         <v>1.04</v>
       </c>
       <c r="V40" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="W40" t="n">
-        <v>2.56</v>
+        <v>4.33</v>
       </c>
       <c r="X40" t="n">
-        <v>2.33</v>
+        <v>1.62</v>
       </c>
       <c r="Y40" t="n">
-        <v>1.54</v>
+        <v>2.25</v>
       </c>
       <c r="Z40" t="n">
-        <v>4.35</v>
+        <v>2.5</v>
       </c>
       <c r="AA40" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AB40" t="n">
-        <v>1.98</v>
+        <v>1.48</v>
       </c>
       <c r="AC40" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AD40" t="inlineStr">
         <is>
@@ -6111,19 +6111,19 @@
         </is>
       </c>
       <c r="AF40" t="n">
-        <v>1.27</v>
+        <v>1.55</v>
       </c>
       <c r="AG40" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="AH40" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="AI40" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AJ40" t="n">
-        <v>4.15</v>
+        <v>2.88</v>
       </c>
       <c r="AK40" t="n">
         <v>0</v>
@@ -6132,10 +6132,10 @@
         <v>0</v>
       </c>
       <c r="AM40" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AN40" t="n">
-        <v>2.4</v>
+        <v>1.91</v>
       </c>
       <c r="AO40" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>BB Erzurumspor</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -6188,83 +6188,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>2.72</v>
+        <v>2.12</v>
       </c>
       <c r="M41" t="n">
-        <v>3.52</v>
+        <v>3.14</v>
       </c>
       <c r="N41" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="O41" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="P41" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="R41" t="n">
         <v>2.44</v>
       </c>
-      <c r="O41" t="n">
-        <v>2</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="R41" t="n">
-        <v>3.25</v>
-      </c>
       <c r="S41" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
       <c r="T41" t="n">
-        <v>1.55</v>
+        <v>1.27</v>
       </c>
       <c r="U41" t="n">
         <v>1.04</v>
       </c>
       <c r="V41" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W41" t="n">
-        <v>4.33</v>
+        <v>2.56</v>
       </c>
       <c r="X41" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF41" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AG41" t="n">
         <v>1.62</v>
       </c>
-      <c r="Y41" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AD41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.45</v>
-      </c>
       <c r="AH41" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="AI41" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AJ41" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="AK41" t="n">
         <v>0</v>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="AM41" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AN41" t="n">
-        <v>1.91</v>
+        <v>2.4</v>
       </c>
       <c r="AO41" s="3" t="n">
         <v>45887.64583333334</v>
@@ -6332,10 +6332,10 @@
         <v>1.5</v>
       </c>
       <c r="M42" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N42" t="n">
-        <v>6.3</v>
+        <v>6.25</v>
       </c>
       <c r="O42" t="n">
         <v>1.5</v>
@@ -6344,40 +6344,40 @@
         <v>3.5</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="R42" t="n">
-        <v>2.35</v>
+        <v>2.29</v>
       </c>
       <c r="S42" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="T42" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="U42" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="V42" t="n">
         <v>1.5</v>
       </c>
       <c r="W42" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="X42" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="Z42" t="n">
         <v>4.92</v>
       </c>
       <c r="AA42" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AB42" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="AC42" t="n">
         <v>1.5</v>
@@ -6393,13 +6393,13 @@
         </is>
       </c>
       <c r="AF42" t="n">
-        <v>1.07</v>
+        <v>1.3</v>
       </c>
       <c r="AG42" t="n">
         <v>2.24</v>
       </c>
       <c r="AH42" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="AI42" t="n">
         <v>2</v>
@@ -6429,12 +6429,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -6444,12 +6444,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>SSC Farul</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Universitatea Cluj</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -6470,98 +6470,98 @@
         </is>
       </c>
       <c r="L43" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="M43" t="n">
-        <v>3.07</v>
+        <v>3.3</v>
       </c>
       <c r="N43" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="O43" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="P43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R43" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="S43" t="n">
+        <v>3</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="V43" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W43" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="X43" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE43" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM43" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="R43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="S43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0</v>
-      </c>
-      <c r="X43" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="Z43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AC43" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE43" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH43" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AI43" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AJ43" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AK43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL43" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM43" t="n">
-        <v>2</v>
-      </c>
       <c r="AN43" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AO43" s="3" t="n">
-        <v>45887.64583333334</v>
+        <v>45887.66666666666</v>
       </c>
     </row>
     <row r="44">
@@ -6575,7 +6575,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Elche CF</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Real Betis</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6611,19 +6611,19 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="M44" t="n">
         <v>3.3</v>
       </c>
       <c r="N44" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="O44" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="P44" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="Q44" t="n">
         <v>1.44</v>
@@ -6632,38 +6632,38 @@
         <v>2.63</v>
       </c>
       <c r="S44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="V44" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="W44" t="n">
         <v>3</v>
       </c>
-      <c r="T44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="U44" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V44" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W44" t="n">
-        <v>3.1</v>
-      </c>
       <c r="X44" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="Z44" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="AA44" t="n">
         <v>1.25</v>
       </c>
       <c r="AB44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC44" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC44" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AD44" t="inlineStr">
         <is>
           <t>[]</t>
@@ -6675,19 +6675,19 @@
         </is>
       </c>
       <c r="AF44" t="n">
-        <v>1.42</v>
+        <v>1.65</v>
       </c>
       <c r="AG44" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH44" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="AI44" t="n">
         <v>2.1</v>
       </c>
       <c r="AJ44" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="AK44" t="n">
         <v>0</v>
@@ -6696,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="AM44" t="n">
-        <v>1.91</v>
+        <v>2.3</v>
       </c>
       <c r="AN44" t="n">
-        <v>2.05</v>
+        <v>1.8</v>
       </c>
       <c r="AO44" s="3" t="n">
         <v>45887.66666666666</v>
@@ -6711,12 +6711,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Elche CF</t>
+          <t>Gil Vicente</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Real Betis</t>
+          <t>Porto</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6752,98 +6752,98 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="M45" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="O45" t="n">
+        <v>3</v>
+      </c>
+      <c r="P45" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="R45" t="n">
+        <v>3</v>
+      </c>
+      <c r="S45" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W45" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="X45" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Z45" t="n">
         <v>3.3</v>
       </c>
-      <c r="N45" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="O45" t="n">
+      <c r="AA45" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AD45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE45" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF45" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AI45" t="n">
         <v>2.3</v>
       </c>
-      <c r="P45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q45" t="n">
+      <c r="AJ45" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>3</v>
+      </c>
+      <c r="AN45" t="n">
         <v>1.44</v>
       </c>
-      <c r="R45" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W45" t="n">
-        <v>3</v>
-      </c>
-      <c r="X45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA45" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC45" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE45" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF45" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AH45" t="n">
-        <v>4</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AJ45" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AK45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL45" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM45" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AN45" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AO45" s="3" t="n">
-        <v>45887.66666666666</v>
+        <v>45887.67708333334</v>
       </c>
     </row>
     <row r="46">
@@ -6857,22 +6857,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Iceland Úrvalsdeild</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Gil Vicente</t>
+          <t>Fram</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Porto</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6893,95 +6893,95 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>5.5</v>
+        <v>2.31</v>
       </c>
       <c r="M46" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N46" t="n">
-        <v>1.55</v>
+        <v>2.51</v>
       </c>
       <c r="O46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P46" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="R46" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W46" t="n">
+        <v>6.18</v>
+      </c>
+      <c r="X46" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Y46" t="n">
         <v>3</v>
       </c>
-      <c r="P46" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q46" t="n">
+      <c r="Z46" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA46" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AB46" t="n">
         <v>1.36</v>
       </c>
-      <c r="R46" t="n">
+      <c r="AC46" t="n">
         <v>3</v>
       </c>
-      <c r="S46" t="n">
+      <c r="AD46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AG46" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH46" t="n">
         <v>2.75</v>
       </c>
-      <c r="T46" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="U46" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="V46" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="W46" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X46" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="Y46" t="n">
+      <c r="AI46" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AJ46" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AK46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL46" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM46" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z46" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AD46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF46" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>2</v>
-      </c>
-      <c r="AK46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL46" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM46" t="n">
-        <v>3</v>
-      </c>
       <c r="AN46" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AO46" s="3" t="n">
         <v>45887.67708333334</v>
@@ -6993,12 +6993,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Iceland Úrvalsdeild</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -7008,12 +7008,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fram</t>
+          <t>Nueva Chicago</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>Central Norte</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -7034,83 +7034,83 @@
         </is>
       </c>
       <c r="L47" t="n">
+        <v>2</v>
+      </c>
+      <c r="M47" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="N47" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="P47" t="n">
         <v>2.75</v>
       </c>
-      <c r="M47" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="N47" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="O47" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P47" t="n">
-        <v>1.91</v>
-      </c>
       <c r="Q47" t="n">
-        <v>1.18</v>
+        <v>1.55</v>
       </c>
       <c r="R47" t="n">
-        <v>4.1</v>
+        <v>2.09</v>
       </c>
       <c r="S47" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="T47" t="n">
-        <v>1.83</v>
+        <v>1.25</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="V47" t="n">
-        <v>1.11</v>
+        <v>1.57</v>
       </c>
       <c r="W47" t="n">
-        <v>6.18</v>
+        <v>2.2</v>
       </c>
       <c r="X47" t="n">
-        <v>1.33</v>
+        <v>2.88</v>
       </c>
       <c r="Y47" t="n">
-        <v>3</v>
+        <v>1.35</v>
       </c>
       <c r="Z47" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AA47" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC47" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE47" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF47" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AG47" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AH47" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="AI47" t="n">
         <v>1.88</v>
       </c>
-      <c r="AA47" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC47" t="n">
-        <v>3</v>
-      </c>
-      <c r="AD47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE47" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF47" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG47" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AH47" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AI47" t="n">
-        <v>2.46</v>
-      </c>
       <c r="AJ47" t="n">
-        <v>3</v>
+        <v>5.08</v>
       </c>
       <c r="AK47" t="n">
         <v>0</v>
@@ -7119,13 +7119,13 @@
         <v>0</v>
       </c>
       <c r="AM47" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AN47" t="n">
-        <v>1.91</v>
+        <v>2.75</v>
       </c>
       <c r="AO47" s="3" t="n">
-        <v>45887.67708333334</v>
+        <v>45887.70833333334</v>
       </c>
     </row>
     <row r="48">
@@ -7134,12 +7134,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -7149,12 +7149,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nueva Chicago</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Central Norte</t>
+          <t>CRB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -7175,58 +7175,58 @@
         </is>
       </c>
       <c r="L48" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="M48" t="n">
-        <v>2.75</v>
+        <v>3.15</v>
       </c>
       <c r="N48" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="O48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="P48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="R48" t="n">
-        <v>2.3</v>
+        <v>2.47</v>
       </c>
       <c r="S48" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T48" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="U48" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="V48" t="n">
-        <v>1.6</v>
+        <v>1.44</v>
       </c>
       <c r="W48" t="n">
-        <v>2.2</v>
+        <v>2.78</v>
       </c>
       <c r="X48" t="n">
-        <v>2.9</v>
+        <v>2.26</v>
       </c>
       <c r="Y48" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="Z48" t="n">
-        <v>5.6</v>
+        <v>4.4</v>
       </c>
       <c r="AA48" t="n">
-        <v>1.13</v>
+        <v>1.2</v>
       </c>
       <c r="AB48" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AC48" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="AD48" t="inlineStr">
         <is>
@@ -7239,19 +7239,19 @@
         </is>
       </c>
       <c r="AF48" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="AG48" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AH48" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="AI48" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AJ48" t="n">
-        <v>5.08</v>
+        <v>3.3</v>
       </c>
       <c r="AK48" t="n">
         <v>0</v>
@@ -7260,13 +7260,13 @@
         <v>0</v>
       </c>
       <c r="AM48" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AN48" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AO48" s="3" t="n">
-        <v>45887.70833333334</v>
+        <v>45887.79166666666</v>
       </c>
     </row>
     <row r="49">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie C</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -7290,12 +7290,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Ypiranga Erechim</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>CRB</t>
+          <t>Botafogo PB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -7316,58 +7316,58 @@
         </is>
       </c>
       <c r="L49" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="M49" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="N49" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O49" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="R49" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="S49" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="V49" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="W49" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="X49" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Y49" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z49" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AA49" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AB49" t="n">
         <v>2.17</v>
       </c>
-      <c r="M49" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="N49" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="R49" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="S49" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="U49" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V49" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="W49" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X49" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="Y49" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z49" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AA49" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>1.87</v>
-      </c>
       <c r="AC49" t="n">
-        <v>1.77</v>
+        <v>1.6</v>
       </c>
       <c r="AD49" t="inlineStr">
         <is>
@@ -7380,19 +7380,19 @@
         </is>
       </c>
       <c r="AF49" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AG49" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="AH49" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="AI49" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AJ49" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="AK49" t="n">
         <v>0</v>
@@ -7401,13 +7401,13 @@
         <v>0</v>
       </c>
       <c r="AM49" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AN49" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AO49" s="3" t="n">
-        <v>45887.79166666666</v>
+        <v>45887.8125</v>
       </c>
     </row>
     <row r="50">
@@ -7431,12 +7431,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ypiranga Erechim</t>
+          <t>Tombense</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Botafogo PB</t>
+          <t>Caxias</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -7457,55 +7457,55 @@
         </is>
       </c>
       <c r="L50" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="R50" t="n">
         <v>2.18</v>
-      </c>
-      <c r="M50" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N50" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="O50" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="P50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R50" t="n">
-        <v>2.22</v>
       </c>
       <c r="S50" t="n">
         <v>3.45</v>
       </c>
       <c r="T50" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="U50" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="V50" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W50" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="X50" t="n">
-        <v>2.37</v>
+        <v>2.62</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="Z50" t="n">
-        <v>4.75</v>
+        <v>5</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="AB50" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="AC50" t="n">
         <v>1.61</v>
@@ -7521,19 +7521,19 @@
         </is>
       </c>
       <c r="AF50" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AG50" t="n">
-        <v>1.68</v>
+        <v>1.31</v>
       </c>
       <c r="AH50" t="n">
-        <v>2.8</v>
+        <v>4.07</v>
       </c>
       <c r="AI50" t="n">
-        <v>1.91</v>
+        <v>1.77</v>
       </c>
       <c r="AJ50" t="n">
-        <v>4.25</v>
+        <v>3.4</v>
       </c>
       <c r="AK50" t="n">
         <v>0</v>
@@ -7542,10 +7542,10 @@
         <v>0</v>
       </c>
       <c r="AM50" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AN50" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AO50" s="3" t="n">
         <v>45887.8125</v>
@@ -7557,12 +7557,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Brazil Serie C</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -7572,12 +7572,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tombense</t>
+          <t>Mirassol</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Caxias</t>
+          <t>Cruzeiro</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -7598,98 +7598,98 @@
         </is>
       </c>
       <c r="L51" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N51" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="O51" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="P51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="R51" t="n">
         <v>2.45</v>
       </c>
-      <c r="M51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="N51" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="O51" t="n">
-        <v>2</v>
-      </c>
-      <c r="P51" t="n">
+      <c r="S51" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="V51" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="W51" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="X51" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Y51" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z51" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AA51" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC51" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE51" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF51" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AG51" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AH51" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AI51" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AJ51" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AK51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL51" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM51" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q51" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="R51" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S51" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="U51" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="V51" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="W51" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="X51" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="Y51" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z51" t="n">
-        <v>5</v>
-      </c>
-      <c r="AA51" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AD51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE51" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF51" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG51" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH51" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AI51" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AJ51" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="AK51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL51" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM51" t="n">
-        <v>2</v>
-      </c>
       <c r="AN51" t="n">
-        <v>2.25</v>
+        <v>1.91</v>
       </c>
       <c r="AO51" s="3" t="n">
-        <v>45887.8125</v>
+        <v>45887.83333333334</v>
       </c>
     </row>
     <row r="52">
@@ -7698,12 +7698,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Ecuador Primera Categoría Serie A</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7713,12 +7713,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Mirassol</t>
+          <t>Deportivo Cuenca</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Cruzeiro</t>
+          <t>Cuniburo</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7739,58 +7739,58 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>3.03</v>
+        <v>1.8</v>
       </c>
       <c r="M52" t="n">
-        <v>2.95</v>
+        <v>3.5</v>
       </c>
       <c r="N52" t="n">
-        <v>2.22</v>
+        <v>4.33</v>
       </c>
       <c r="O52" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="P52" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="R52" t="n">
-        <v>2.45</v>
+        <v>2.63</v>
       </c>
       <c r="S52" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T52" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="U52" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="V52" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W52" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="X52" t="n">
-        <v>2.07</v>
+        <v>2.15</v>
       </c>
       <c r="Y52" t="n">
         <v>1.67</v>
       </c>
       <c r="Z52" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AC52" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AD52" t="inlineStr">
         <is>
@@ -7803,19 +7803,19 @@
         </is>
       </c>
       <c r="AF52" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AG52" t="n">
-        <v>1.36</v>
+        <v>1.95</v>
       </c>
       <c r="AH52" t="n">
-        <v>3.75</v>
+        <v>2.5</v>
       </c>
       <c r="AI52" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AJ52" t="n">
-        <v>2.89</v>
+        <v>5</v>
       </c>
       <c r="AK52" t="n">
         <v>0</v>
@@ -7824,13 +7824,13 @@
         <v>0</v>
       </c>
       <c r="AM52" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AN52" t="n">
-        <v>1.91</v>
+        <v>2.63</v>
       </c>
       <c r="AO52" s="3" t="n">
-        <v>45887.83333333334</v>
+        <v>45887.875</v>
       </c>
     </row>
     <row r="53">
@@ -7980,12 +7980,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ecuador Primera Categoría Serie A</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7995,12 +7995,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Deportivo Cuenca</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Cuniburo</t>
+          <t>Chicago Red Stars</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -8021,59 +8021,59 @@
         </is>
       </c>
       <c r="L54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="M54" t="n">
+        <v>4.09</v>
+      </c>
+      <c r="N54" t="n">
+        <v>5.78</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="R54" t="n">
+        <v>3</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="V54" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="W54" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="X54" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="Y54" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Z54" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA54" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB54" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC54" t="n">
         <v>1.8</v>
       </c>
-      <c r="M54" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N54" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="R54" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="S54" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V54" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="W54" t="n">
-        <v>3</v>
-      </c>
-      <c r="X54" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Y54" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Z54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA54" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AB54" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC54" t="n">
-        <v>1.73</v>
-      </c>
       <c r="AD54" t="inlineStr">
         <is>
           <t>[]</t>
@@ -8085,19 +8085,19 @@
         </is>
       </c>
       <c r="AF54" t="n">
-        <v>1.2</v>
+        <v>1.06</v>
       </c>
       <c r="AG54" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AH54" t="n">
         <v>1.95</v>
       </c>
-      <c r="AH54" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AI54" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AJ54" t="n">
-        <v>5</v>
+        <v>5.9</v>
       </c>
       <c r="AK54" t="n">
         <v>0</v>
@@ -8106,153 +8106,12 @@
         <v>0</v>
       </c>
       <c r="AM54" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AN54" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AO54" s="3" t="n">
-        <v>45887.875</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="2" t="n">
-        <v>45887</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Chicago Red Stars</t>
-        </is>
-      </c>
-      <c r="G55" t="n">
-        <v>0</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L55" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="M55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N55" t="n">
-        <v>5</v>
-      </c>
-      <c r="O55" t="n">
-        <v>0</v>
-      </c>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="R55" t="n">
-        <v>3</v>
-      </c>
-      <c r="S55" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="U55" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V55" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W55" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="X55" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="Y55" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Z55" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA55" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC55" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF55" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AG55" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AH55" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AI55" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AJ55" t="n">
-        <v>6.16</v>
-      </c>
-      <c r="AK55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN55" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO55" s="3" t="n">
         <v>45887.95833333334</v>
       </c>
     </row>

--- a/jogos_2025-08-18.xlsx
+++ b/jogos_2025-08-18.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO54"/>
+  <dimension ref="A1:AO55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -935,22 +935,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Saham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Bahla</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1076,22 +1076,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Saham</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bahla</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ukraine Ukrainian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1368,12 +1368,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Zorya</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Salt</t>
+          <t>Hirnyk</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1394,58 +1394,58 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
@@ -1458,19 +1458,19 @@
         </is>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AO7" s="3" t="n">
         <v>45887.5</v>
@@ -1499,7 +1499,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ukraine Ukrainian Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1509,12 +1509,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zorya</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Hirnyk</t>
+          <t>Al Salt</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1535,58 +1535,58 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.27</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
@@ -1599,19 +1599,19 @@
         </is>
       </c>
       <c r="AF8" t="n">
-        <v>1.46</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
@@ -1620,10 +1620,10 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AO8" s="3" t="n">
         <v>45887.5</v>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zob Ahan</t>
+          <t>Gol Gohar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paykan</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1791,12 +1791,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gol Gohar</t>
+          <t>Zob Ahan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Paykan</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1922,22 +1922,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Persepolis</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Fajr Sepasi</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1958,58 +1958,58 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>5.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
@@ -2043,10 +2043,10 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2063,22 +2063,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gareji</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2345,22 +2345,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Dobrudzha 1919</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2381,83 +2381,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.74</v>
+        <v>2.76</v>
       </c>
       <c r="M14" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="N14" t="n">
-        <v>1.9</v>
+        <v>2.42</v>
       </c>
       <c r="O14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="P14" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.26</v>
+        <v>1.44</v>
       </c>
       <c r="R14" t="n">
-        <v>3.28</v>
+        <v>2.62</v>
       </c>
       <c r="S14" t="n">
-        <v>2.32</v>
+        <v>3.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="U14" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="V14" t="n">
-        <v>1.17</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>5.04</v>
+        <v>2.75</v>
       </c>
       <c r="X14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AG14" t="n">
         <v>1.5</v>
       </c>
-      <c r="Y14" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF14" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI14" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AJ14" t="n">
-        <v>2.43</v>
+        <v>3.5</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
@@ -2466,10 +2466,10 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AN14" t="n">
-        <v>1.62</v>
+        <v>2.05</v>
       </c>
       <c r="AO14" s="3" t="n">
         <v>45887.54166666666</v>
@@ -2486,7 +2486,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2496,12 +2496,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem</t>
+          <t>Persepolis</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Fajr Sepasi</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2627,22 +2627,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dobrudzha 1919</t>
+          <t>Gareji</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2663,58 +2663,58 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
@@ -2727,19 +2727,19 @@
         </is>
       </c>
       <c r="AF16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AK16" t="n">
         <v>0</v>
@@ -2748,10 +2748,10 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AO16" s="3" t="n">
         <v>45887.54166666666</v>
@@ -3086,13 +3086,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.97</v>
+        <v>2.7</v>
       </c>
       <c r="M19" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.46</v>
+        <v>2.7</v>
       </c>
       <c r="O19" t="n">
         <v>2.31</v>
@@ -3122,16 +3122,16 @@
         <v>2.6</v>
       </c>
       <c r="X19" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="Z19" t="n">
         <v>4.45</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="AB19" t="n">
         <v>1.99</v>
@@ -3156,10 +3156,10 @@
         <v>1.34</v>
       </c>
       <c r="AH19" t="n">
-        <v>3.84</v>
+        <v>3.75</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.97</v>
+        <v>1.91</v>
       </c>
       <c r="AJ19" t="n">
         <v>2.99</v>
@@ -3191,7 +3191,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Sweden Allsvenskan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Agropecuario</t>
+          <t>Värnamo</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Club Atlético Mitre</t>
+          <t>Degerfors</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3227,59 +3227,59 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.15</v>
+        <v>2.26</v>
       </c>
       <c r="M20" t="n">
-        <v>2.7</v>
+        <v>3.21</v>
       </c>
       <c r="N20" t="n">
-        <v>3.63</v>
+        <v>2.73</v>
       </c>
       <c r="O20" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="P20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="R20" t="n">
-        <v>2.12</v>
+        <v>3.25</v>
       </c>
       <c r="S20" t="n">
-        <v>4.3</v>
+        <v>2.63</v>
       </c>
       <c r="T20" t="n">
-        <v>1.16</v>
+        <v>1.44</v>
       </c>
       <c r="U20" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="V20" t="n">
-        <v>1.65</v>
+        <v>1.25</v>
       </c>
       <c r="W20" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC20" t="n">
         <v>2.2</v>
       </c>
-      <c r="X20" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>6</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.48</v>
-      </c>
       <c r="AD20" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3291,19 +3291,19 @@
         </is>
       </c>
       <c r="AF20" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AH20" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.93</v>
+        <v>2.25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.82</v>
+        <v>3.25</v>
       </c>
       <c r="AK20" t="n">
         <v>0</v>
@@ -3312,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AN20" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="AO20" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3332,22 +3332,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group B</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3368,58 +3368,58 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AD21" t="inlineStr">
         <is>
@@ -3432,19 +3432,19 @@
         </is>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK21" t="n">
         <v>0</v>
@@ -3453,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AO21" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3483,12 +3483,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3509,31 +3509,31 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.84</v>
+        <v>2.02</v>
       </c>
       <c r="M22" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="N22" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
         <v>1.3</v>
       </c>
       <c r="R22" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="S22" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="U22" t="n">
         <v>1.03</v>
@@ -3542,25 +3542,25 @@
         <v>1.17</v>
       </c>
       <c r="W22" t="n">
-        <v>3.98</v>
+        <v>4.2</v>
       </c>
       <c r="X22" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="AD22" t="inlineStr">
         <is>
@@ -3573,19 +3573,19 @@
         </is>
       </c>
       <c r="AF22" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.3</v>
+        <v>2.39</v>
       </c>
       <c r="AJ22" t="n">
-        <v>4.33</v>
+        <v>3.25</v>
       </c>
       <c r="AK22" t="n">
         <v>0</v>
@@ -3594,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AN22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="AO22" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Russia Russian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Olimpiyets</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Makhachkala</t>
+          <t>AGF</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3650,58 +3650,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="M23" t="n">
-        <v>2.88</v>
+        <v>3.6</v>
       </c>
       <c r="N23" t="n">
-        <v>2.84</v>
+        <v>2.18</v>
       </c>
       <c r="O23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="Q23" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="R23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W23" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.57</v>
       </c>
-      <c r="R23" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="S23" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="T23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="W23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.35</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.52</v>
+        <v>2.25</v>
       </c>
       <c r="Z23" t="n">
-        <v>4.65</v>
+        <v>2.45</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="AB23" t="n">
-        <v>2.04</v>
+        <v>1.55</v>
       </c>
       <c r="AC23" t="n">
-        <v>1.69</v>
+        <v>2.42</v>
       </c>
       <c r="AD23" t="inlineStr">
         <is>
@@ -3714,19 +3714,19 @@
         </is>
       </c>
       <c r="AF23" t="n">
-        <v>1.46</v>
+        <v>1.3</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.48</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.9</v>
+        <v>2.29</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.64</v>
+        <v>2.64</v>
       </c>
       <c r="AK23" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         <v>0</v>
       </c>
       <c r="AM23" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AN23" t="n">
-        <v>2.15</v>
+        <v>1.8</v>
       </c>
       <c r="AO23" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3755,22 +3755,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group D</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vianense</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3791,58 +3791,58 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>6.89</v>
       </c>
       <c r="AK24" t="n">
         <v>0</v>
@@ -3876,10 +3876,10 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AO24" s="3" t="n">
         <v>45887.58333333334</v>
@@ -3896,22 +3896,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>AGF</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3932,58 +3932,58 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.04</v>
+        <v>1.33</v>
       </c>
       <c r="M25" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="N25" t="n">
-        <v>2.18</v>
+        <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
@@ -3996,19 +3996,19 @@
         </is>
       </c>
       <c r="AF25" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="AJ25" t="n">
-        <v>2.64</v>
+        <v>0</v>
       </c>
       <c r="AK25" t="n">
         <v>0</v>
@@ -4017,10 +4017,10 @@
         <v>0</v>
       </c>
       <c r="AM25" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AN25" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AO25" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4047,12 +4047,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -4073,83 +4073,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.03</v>
+        <v>1.84</v>
       </c>
       <c r="M26" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.95</v>
+        <v>3.75</v>
       </c>
       <c r="O26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="W26" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF26" t="n">
         <v>1.25</v>
       </c>
-      <c r="R26" t="n">
-        <v>4</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W26" t="n">
-        <v>5</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.7</v>
+        <v>1.85</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
       <c r="AI26" t="n">
         <v>2.3</v>
       </c>
       <c r="AJ26" t="n">
-        <v>3</v>
+        <v>4.33</v>
       </c>
       <c r="AK26" t="n">
         <v>0</v>
@@ -4158,10 +4158,10 @@
         <v>0</v>
       </c>
       <c r="AM26" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="AN26" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="AO26" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4178,22 +4178,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Portugal Campeonato de Portugal Group B</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Vianense</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -4214,58 +4214,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="inlineStr">
         <is>
@@ -4278,19 +4278,19 @@
         </is>
       </c>
       <c r="AF27" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="AJ27" t="n">
-        <v>6.89</v>
+        <v>0</v>
       </c>
       <c r="AK27" t="n">
         <v>0</v>
@@ -4299,10 +4299,10 @@
         <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AO27" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4319,22 +4319,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4355,58 +4355,58 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="M28" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>7</v>
+        <v>4.9</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AD28" t="inlineStr">
         <is>
@@ -4419,19 +4419,19 @@
         </is>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AK28" t="n">
         <v>0</v>
@@ -4440,10 +4440,10 @@
         <v>0</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AO28" s="3" t="n">
         <v>45887.58333333334</v>
@@ -4460,22 +4460,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sweden Allsvenskan</t>
+          <t>Russia Russian Premier League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Värnamo</t>
+          <t>Olimpiyets</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Degerfors</t>
+          <t>Makhachkala</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4496,58 +4496,58 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.26</v>
+        <v>2.7</v>
       </c>
       <c r="M29" t="n">
-        <v>3.21